--- a/data/raw/evidence/TPBank.xlsx
+++ b/data/raw/evidence/TPBank.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="1263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="1266">
   <si>
     <t>PHIẾU THU THẬP MINH CHỨNG &amp; CHẤM ĐIỂM CĐS (DBI)</t>
   </si>
@@ -30,90 +30,90 @@
     <t>Ngân hàng</t>
   </si>
   <si>
+    <t>Nhóm tiêu chí</t>
+  </si>
+  <si>
+    <t>Mã</t>
+  </si>
+  <si>
+    <t>Tiêu chí</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
     <t>TPBank</t>
   </si>
   <si>
-    <t>Nhóm tiêu chí</t>
-  </si>
-  <si>
-    <t>Mã</t>
-  </si>
-  <si>
-    <t>Tiêu chí</t>
-  </si>
-  <si>
-    <t>Level</t>
+    <t>Minh chứng</t>
+  </si>
+  <si>
+    <t>Nguồn</t>
+  </si>
+  <si>
+    <t>Trang</t>
+  </si>
+  <si>
+    <t>Năm</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Mức 1</t>
   </si>
   <si>
     <t>← Tên ngân hàng: KHÔNG sửa (code đọc ô B3 để nhận diện)</t>
   </si>
   <si>
-    <t>Minh chứng</t>
+    <t>Mức 2</t>
+  </si>
+  <si>
+    <t>Mức 3</t>
+  </si>
+  <si>
+    <t>Mức 4</t>
   </si>
   <si>
     <t>Người phụ trách</t>
   </si>
   <si>
+    <t>Mức 5</t>
+  </si>
+  <si>
     <t>Thư</t>
   </si>
   <si>
-    <t>Nguồn</t>
-  </si>
-  <si>
     <t>Năm dữ liệu (FY)</t>
   </si>
   <si>
-    <t>Trang</t>
+    <t>1. Trụ cột Khách hàng</t>
   </si>
   <si>
     <t>Deadline nộp</t>
   </si>
   <si>
-    <t>Năm</t>
-  </si>
-  <si>
-    <t>Ghi chú</t>
-  </si>
-  <si>
     <t>09/10</t>
   </si>
   <si>
-    <t>Mức 1</t>
-  </si>
-  <si>
     <t>CÁCH ĐIỀN (sheet "Chấm điểm")</t>
   </si>
   <si>
-    <t>Mức 2</t>
+    <t>Góc nhìn của khách hàng đối với sản phẩm, dịch vụ</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>1. Chỉ điền vào các cột nền VÀNG (Level, Minh chứng, Nguồn, Trang, Năm, Ghi chú). Cột xám là cố định, không sửa.</t>
   </si>
   <si>
-    <t>Mức 3</t>
-  </si>
-  <si>
-    <t>Mức 4</t>
-  </si>
-  <si>
-    <t>Mức 5</t>
-  </si>
-  <si>
-    <t>1. Trụ cột Khách hàng</t>
-  </si>
-  <si>
-    <t>Góc nhìn của khách hàng đối với sản phẩm, dịch vụ</t>
-  </si>
-  <si>
-    <t>1.1.1</t>
+    <t>Cá nhân hóa trải nghiệm</t>
   </si>
   <si>
     <t>2. Đọc mô tả Mức 1–5 ở các cột bên phải của từng tiêu chí, rồi đọc minh chứng đã ghi để chọn Level.</t>
   </si>
   <si>
-    <t>Cá nhân hóa trải nghiệm</t>
-  </si>
-  <si>
     <t>3. Level: chọn từ danh sách 1, 2, 3, 4, 5 hoặc N/A (không có minh chứng công khai). Không để trống.</t>
   </si>
   <si>
@@ -126,24 +126,24 @@
     <t>6. Nguồn: tên tài liệu hoặc URL. Nhiều nguồn thì cách nhau bằng dấu chấm phẩy ( ; ). Ưu tiên BCTN, BC PTBV, website ngân hàng hơn tin tức.</t>
   </si>
   <si>
+    <t>7. Trang: số trang trong tài liệu (nếu là website thì ghi "web"). Năm: năm của tài liệu/bài đăng.</t>
+  </si>
+  <si>
+    <t>8. Chỉ dùng dữ liệu công khai. Chấm theo minh chứng đã ghi, không chấm theo ấn tượng chung về ngân hàng.</t>
+  </si>
+  <si>
+    <t>9. Không thêm/xóa/đổi thứ tự dòng, không đổi tên cột, không đổi mã tiêu chí (phải đủ 140 mã).</t>
+  </si>
+  <si>
     <t>TPBank triển khai Data-First, sử dụng dữ liệu để cá nhân hóa trải nghiệm; các tính năng được thiết kế theo hành vi và nhu cầu người dùng.</t>
   </si>
   <si>
-    <t>7. Trang: số trang trong tài liệu (nếu là website thì ghi "web"). Năm: năm của tài liệu/bài đăng.</t>
-  </si>
-  <si>
-    <t>8. Chỉ dùng dữ liệu công khai. Chấm theo minh chứng đã ghi, không chấm theo ấn tượng chung về ngân hàng.</t>
+    <t>VÍ DỤ ĐIỀN (chỉ minh họa, KHÔNG chép vào sheet Chấm điểm)</t>
   </si>
   <si>
     <t>https://tpb.vn/tin-tuc/tin-tpbank/cham-tuong-lai-nganh-tai-chinh-cung-ngan-hang-tri-tue-tpbank</t>
   </si>
   <si>
-    <t>9. Không thêm/xóa/đổi thứ tự dòng, không đổi tên cột, không đổi mã tiêu chí (phải đủ 140 mã).</t>
-  </si>
-  <si>
-    <t>VÍ DỤ ĐIỀN (chỉ minh họa, KHÔNG chép vào sheet Chấm điểm)</t>
-  </si>
-  <si>
     <t>Ứng dụng gợi ý sản phẩm/ưu đãi theo hành vi giao dịch cho nhóm khách hàng cá nhân; chưa nêu phạm vi toàn ngân hàng.</t>
   </si>
   <si>
@@ -195,6 +195,9 @@
     <t>https://tpb.vn/wps/wcm/connect/71611b1e-e466-4eb5-a468-1d9f33d0df09/BCTN+2026+TV+21.4+VIEW+%281%29.pdf?MOD=AJPERES&amp;CONVERT_TO=url&amp;CACHEID=ROOTWORKSPACE-71611b1e-e466-4eb5-a468-1d9f33d0df09-pSU5qGp</t>
   </si>
   <si>
+    <t>2. Trụ cột Chiến lược</t>
+  </si>
+  <si>
     <t>Có một số nội dung tiếp thị được nhắm mục tiêu.</t>
   </si>
   <si>
@@ -222,6 +225,9 @@
     <t>https://tpb.vn/tin-tuc/tin-tpbank/paste-to-pay-cong-nghe-chuyen-tien-doc-dao-tu-tpbank</t>
   </si>
   <si>
+    <t>3. Trụ cột Công nghệ</t>
+  </si>
+  <si>
     <t>Có rất ít công cụ sẵn có để cho phép khách hàng tùy chỉnh sản phẩm và dịch vụ.</t>
   </si>
   <si>
@@ -270,12 +276,12 @@
     <t>TPBank công bố các sản phẩm số được phát triển để tạo trải nghiệm khác biệt, đặc biệt hướng tới nhóm khách hàng trẻ.</t>
   </si>
   <si>
-    <t>2. Trụ cột Chiến lược</t>
-  </si>
-  <si>
     <t>https://tpb.vn/tin-tuc/tin-tpbank/khac-biet-lam-nen-suc-hut-cua-cac-dich-vu-ngan-hang-so-tpbank</t>
   </si>
   <si>
+    <t>4. Trụ cột Vận hành</t>
+  </si>
+  <si>
     <t>Có rất ít hoạt động tương tác của khách hàng với doanh nghiệp khiến khách hàng cảm thấy thú vị.</t>
   </si>
   <si>
@@ -300,6 +306,9 @@
     <t>ChatPay, VoicePay, T’Aio và App TPBank tạo nhiều hình thức tương tác số với khách hàng.</t>
   </si>
   <si>
+    <t>5. Trụ cột Văn hóa</t>
+  </si>
+  <si>
     <t>Có rất ít tương tác có thể được thực hiện trên các kênh số.</t>
   </si>
   <si>
@@ -315,9 +324,6 @@
     <t>Tất cả các tương tác của khách hàng với doanh nghiệp và các đối tác trong hệ sinh thái của doanh nghiệp có thể được thực hiện trên các kênh số.</t>
   </si>
   <si>
-    <t>3. Trụ cột Công nghệ</t>
-  </si>
-  <si>
     <t>1.1.7</t>
   </si>
   <si>
@@ -351,6 +357,9 @@
     <t>ChatPay được TPBank phát triển theo hướng đưa hoạt động ngân hàng vào môi trường giao tiếp quen thuộc; sản phẩm được trao giải Best Social Banking Initiative.</t>
   </si>
   <si>
+    <t>6. Trụ cột Dữ liệu</t>
+  </si>
+  <si>
     <t>Sự gắn kết xã hội chưa được xem xét.</t>
   </si>
   <si>
@@ -375,9 +384,6 @@
     <t>TPBank phát triển hệ sinh thái số, các chương trình/đặc quyền và trải nghiệm riêng cho các phân khúc khách hàng.</t>
   </si>
   <si>
-    <t>4. Trụ cột Vận hành</t>
-  </si>
-  <si>
     <t>Các chương trình thúc đẩy sự trung thành chưa được doanh nghiệp tích cực xem xét.</t>
   </si>
   <si>
@@ -408,6 +414,9 @@
     <t>Doanh nghiệp chưa có bất kỳ tầm nhìn về trải nghiệm khách hàng.</t>
   </si>
   <si>
+    <t>TỔNG</t>
+  </si>
+  <si>
     <t>Một số bộ phận, đơn vị chức năng đã bắt đầu xác định tầm nhìn về trải nghiệm của khách hàng.</t>
   </si>
   <si>
@@ -453,9 +462,6 @@
     <t>TPBank có đầu tư vào AI, Big Data, Cloud, Core Banking và hạ tầng số; không công bố riêng một khoản ngân sách cho mục tiêu CX trong nguồn đã kiểm tra.</t>
   </si>
   <si>
-    <t>5. Trụ cột Văn hóa</t>
-  </si>
-  <si>
     <t>Doanh nghiệp chưa có kế hoạch đầu tư để đạt được tầm nhìn trải nghiệm của khách hàng.</t>
   </si>
   <si>
@@ -471,6 +477,9 @@
     <t>Toàn bộ bộ phận, đơn vị chức năng có liên quan đến khách hàng và hệ sinh thái có kế hoạch đầu tư để đạt được tầm nhìn về trải nghiệm của khách hàng.</t>
   </si>
   <si>
+    <t>Level sai (khác 1–5 và N/A)</t>
+  </si>
+  <si>
     <t>1.2.4</t>
   </si>
   <si>
@@ -483,9 +492,6 @@
     <t>https://tpb.vn/tin-tuc/tin-tpbank/tpbank-mo-rong-he-sinh-thai-thanh-toan-so-theo-khach-hang-ra-the-gioi-dua-the-gioi-den-gan-voi-doanh-nghiep-viet</t>
   </si>
   <si>
-    <t>6. Trụ cột Dữ liệu</t>
-  </si>
-  <si>
     <t>Trải nghiệm khách hàng chưa được xem xét trong phát triển danh mục sản phẩm và dịch vụ.</t>
   </si>
   <si>
@@ -501,6 +507,9 @@
     <t>Trải nghiệm của khách hàng là một phần không thể thiếu trong danh mục sản phẩm và dịch vụ do doanh nghiệp và các đối tác trong hệ sinh thái của doanh nghiệp cung cấp.</t>
   </si>
   <si>
+    <t>Có Level 1–5 nhưng thiếu Minh chứng</t>
+  </si>
+  <si>
     <t>1.2.5</t>
   </si>
   <si>
@@ -546,6 +555,9 @@
     <t>Doanh nghiệp quản lý được bối cảnh của toàn bộ các hành trình khách hàng liên thông trên tất cả các kênh và thiết bị.</t>
   </si>
   <si>
+    <t>Có Level 1–5 nhưng thiếu Nguồn</t>
+  </si>
+  <si>
     <t>Doanh nghiệp và hệ sinh thái quản lý được bối cảnh của toàn bộ các hành trình khách hàng liên thông trên tất cả các kênh và thiết bị.</t>
   </si>
   <si>
@@ -561,7 +573,7 @@
     <t>https://dantri.com.vn/kinh-doanh/tpbank-dat-chuan-quoc-te-icxs2019-ve-trai-nghiem-khach-hang-20260409100317065.htm</t>
   </si>
   <si>
-    <t>TỔNG</t>
+    <t>Mục tiêu: "Còn trống" = 0 và cả 3 ô kiểm tra = 0 trước khi nộp.</t>
   </si>
   <si>
     <t>Hiệu suất hành trình khách hàng chưa được đo lường.</t>
@@ -588,9 +600,6 @@
     <t>TPBank phát triển sản phẩm dựa trên hành vi và nhu cầu khách hàng; tuy nhiên chưa có công bố năm 2025 mô tả đầy đủ một hệ thống quản lý customer journey toàn ngân hàng.</t>
   </si>
   <si>
-    <t>Level sai (khác 1–5 và N/A)</t>
-  </si>
-  <si>
     <t>Hiệu suất của hành trình của khách hàng chưa được quản lý.</t>
   </si>
   <si>
@@ -639,9 +648,6 @@
     <t>1.3.2</t>
   </si>
   <si>
-    <t>Có Level 1–5 nhưng thiếu Minh chứng</t>
-  </si>
-  <si>
     <t>Nguồn khai thác dữ liệu tin cậy duy nhất</t>
   </si>
   <si>
@@ -663,9 +669,6 @@
     <t>Có một nguồn tin cậy duy nhất cho toàn bộ thông tin khách hàng trong toàn doanh nghiệp.</t>
   </si>
   <si>
-    <t>Có Level 1–5 nhưng thiếu Nguồn</t>
-  </si>
-  <si>
     <t>Có một nguồn tin cậy duy nhất cho toàn bộ thông tin khách hàng trong toàn doanh nghiệp và các đối tác trong hệ sinh thái của doanh nghiệp.</t>
   </si>
   <si>
@@ -702,9 +705,6 @@
     <t>Cam kết thương hiệu</t>
   </si>
   <si>
-    <t>Mục tiêu: "Còn trống" = 0 và cả 3 ô kiểm tra = 0 trước khi nộp.</t>
-  </si>
-  <si>
     <t>TPBank duy trì định vị ngân hàng số, lấy công nghệ và trải nghiệm làm trọng tâm; hơn 98% giao dịch khách hàng qua kênh số được công bố trong năm 2025.</t>
   </si>
   <si>
@@ -888,6 +888,12 @@
     <t>Chỉ số đo lường thương hiệu</t>
   </si>
   <si>
+    <t>Brand Finance Vietnam 100 ghi nhận Chỉ số Sức mạnh Thương hiệu (BSI) của TPBank tăng mạnh lên 73.9/100 (xếp hạng AA). Các chỉ số cấu thành độ phủ kỹ thuật số như “mức độ quen thuộc thương hiệu” tăng từ 25% lên 42%, và điểm số thuộc tính “Đổi mới sáng tạo (Innovation)” đạt mức gần tuyệt đối 9.9/10.</t>
+  </si>
+  <si>
+    <t>https://tpb.vn/tin-tuc/tin-tpbank/tpbank-va-con-duong-xay-dung-thuong-hieu-cong-nghe-ngan-hang-so-dam-chat-bank-tim</t>
+  </si>
+  <si>
     <t>Chỉ số phản ánh hoạt động của thương hiệu số được đo lường theo sự vụ.</t>
   </si>
   <si>
@@ -966,6 +972,9 @@
     <t>Thiết kế hệ sinh thái</t>
   </si>
   <si>
+    <t>TPBank là một trong những ngân hàng tiên phong tại Việt Nam làm chủ mô hình Open Banking (Ngân hàng mở) thông qua hệ thống kết nối API mở. Thay vì chỉ cung cấp dịch vụ ngân hàng truyền thống, TPBank tích hợp sâu năng lực xử lý tài chính của mình vào các ngành công nghiệp khác như Thương mại điện tử (Shopee, Lazada), Gọi xe/Giao hàng (Grab, Be), và các Ví điện tử (Momo, VNPAY).</t>
+  </si>
+  <si>
     <t>Doanh nghiệp chưa bắt đầu thiết kế hệ sinh thái.</t>
   </si>
   <si>
@@ -987,7 +996,7 @@
     <t>Lựa chọn đối tác</t>
   </si>
   <si>
-    <t>Quy trình lựa chọn đối tác hệ sinh thái chặt chẽ dựa trên uy tín, năng lực công nghệ và tiêu chuẩn an toàn bảo mật thông tin.</t>
+    <t>Quy trình lựa chọn đối tác hệ sinh thái chặt chẽ dựa trên uy tín, năng lực công nghệ và tiêu chuẩn an toàn bảo mật thông tin. Thay vì chỉ cung cấp dịch vụ ngân hàng truyền thống, TPBank tích hợp sâu năng lực xử lý tài chính của mình vào các ngành công nghiệp khác như Thương mại điện tử (Shopee, Lazada), Gọi xe/Giao hàng (Grab, Be), và các Ví điện tử (Momo, VNPAY).</t>
   </si>
   <si>
     <t>Doanh nghiệp chưa chọn đối tác như một phần của hệ sinh thái.</t>
@@ -5073,14 +5082,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
-      <color theme="1"/>
+      <sz val="10.0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11.0"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -5095,14 +5104,14 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <sz val="12.0"/>
       <color rgb="FF1F3864"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -5155,14 +5164,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FFBF8F00"/>
+        <bgColor rgb="FFBF8F00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBF8F00"/>
-        <bgColor rgb="FFBF8F00"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -5235,40 +5244,40 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -5277,29 +5286,26 @@
     <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="1" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -5307,34 +5313,37 @@
     <xf borderId="1" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="11" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="11" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -5589,118 +5598,118 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>8</v>
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>11</v>
+      <c r="A4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="4">
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="5">
         <v>2025.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>18</v>
+      <c r="A6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>20</v>
+      <c r="A8" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9" ht="30.0" customHeight="1">
-      <c r="A9" s="10" t="s">
-        <v>22</v>
+      <c r="A9" s="11" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="10" ht="30.0" customHeight="1">
-      <c r="A10" s="10" t="s">
-        <v>29</v>
+      <c r="A10" s="11" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11" ht="30.0" customHeight="1">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="11" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="12" ht="30.0" customHeight="1">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" ht="30.0" customHeight="1">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="11" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" ht="30.0" customHeight="1">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" ht="30.0" customHeight="1">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" ht="30.0" customHeight="1">
+      <c r="A16" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" ht="30.0" customHeight="1">
-      <c r="A16" s="10" t="s">
+    <row r="17" ht="30.0" customHeight="1">
+      <c r="A17" s="11" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" ht="30.0" customHeight="1">
-      <c r="A17" s="10" t="s">
+    <row r="19">
+      <c r="A19" s="9" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="14" t="s">
-        <v>12</v>
-      </c>
       <c r="E20" s="14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" ht="54.75" customHeight="1">
       <c r="A21" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="15">
         <v>3.0</v>
@@ -5735,30 +5744,30 @@
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="9" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="16" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="20" t="s">
-        <v>26</v>
+      <c r="A27" s="17" t="s">
+        <v>22</v>
       </c>
       <c r="B27" s="22">
         <f>COUNTIF('Chấm điểm'!$A$2:$A$141,A27)</f>
@@ -5778,8 +5787,8 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="20" t="s">
-        <v>83</v>
+      <c r="A28" s="17" t="s">
+        <v>58</v>
       </c>
       <c r="B28" s="22">
         <f>COUNTIF('Chấm điểm'!$A$2:$A$141,A28)</f>
@@ -5787,7 +5796,7 @@
       </c>
       <c r="C28" s="22">
         <f>COUNTIFS('Chấm điểm'!$A$2:$A$141,A28,'Chấm điểm'!$E$2:$E$141,"&gt;=1",'Chấm điểm'!$E$2:$E$141,"&lt;=5")</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D28" s="22">
         <f>COUNTIFS('Chấm điểm'!$A$2:$A$141,A28,'Chấm điểm'!$E$2:$E$141,"N/A")</f>
@@ -5795,12 +5804,12 @@
       </c>
       <c r="E28" s="22">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="20" t="s">
-        <v>98</v>
+      <c r="A29" s="17" t="s">
+        <v>68</v>
       </c>
       <c r="B29" s="22">
         <f>COUNTIF('Chấm điểm'!$A$2:$A$141,A29)</f>
@@ -5820,8 +5829,8 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="20" t="s">
-        <v>118</v>
+      <c r="A30" s="17" t="s">
+        <v>86</v>
       </c>
       <c r="B30" s="22">
         <f>COUNTIF('Chấm điểm'!$A$2:$A$141,A30)</f>
@@ -5841,8 +5850,8 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="20" t="s">
-        <v>144</v>
+      <c r="A31" s="17" t="s">
+        <v>95</v>
       </c>
       <c r="B31" s="22">
         <f>COUNTIF('Chấm điểm'!$A$2:$A$141,A31)</f>
@@ -5862,8 +5871,8 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="20" t="s">
-        <v>154</v>
+      <c r="A32" s="17" t="s">
+        <v>112</v>
       </c>
       <c r="B32" s="22">
         <f>COUNTIF('Chấm điểm'!$A$2:$A$141,A32)</f>
@@ -5883,30 +5892,30 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="B33" s="25">
+      <c r="A33" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B33" s="24">
         <f t="shared" ref="B33:E33" si="2">SUM(B27:B32)</f>
         <v>140</v>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="24">
         <f t="shared" si="2"/>
-        <v>116</v>
-      </c>
-      <c r="D33" s="25">
+        <v>118</v>
+      </c>
+      <c r="D33" s="24">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="E33" s="25">
+      <c r="E33" s="24">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="26" t="s">
-        <v>189</v>
+      <c r="A35" s="25" t="s">
+        <v>152</v>
       </c>
       <c r="D35" s="27">
         <f>COUNTA('Chấm điểm'!$E$2:$E$141)-COUNT('Chấm điểm'!$E$2:$E$141)-COUNTIF('Chấm điểm'!$E$2:$E$141,"N/A")+COUNT('Chấm điểm'!$E$2:$E$141)-COUNTIFS('Chấm điểm'!$E$2:$E$141,"&gt;=1",'Chấm điểm'!$E$2:$E$141,"&lt;=5")</f>
@@ -5914,8 +5923,8 @@
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="26" t="s">
-        <v>206</v>
+      <c r="A36" s="25" t="s">
+        <v>162</v>
       </c>
       <c r="D36" s="27">
         <f>SUMPRODUCT(ISNUMBER('Chấm điểm'!$E$2:$E$141)*('Chấm điểm'!$F$2:$F$141=""))</f>
@@ -5923,17 +5932,17 @@
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="26" t="s">
-        <v>214</v>
+      <c r="A37" s="25" t="s">
+        <v>178</v>
       </c>
       <c r="D37" s="27">
         <f>SUMPRODUCT(ISNUMBER('Chấm điểm'!$E$2:$E$141)*('Chấm điểm'!$G$2:$G$141=""))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="6" t="s">
-        <v>227</v>
+      <c r="A38" s="7" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1"/>
@@ -6948,79 +6957,79 @@
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="5" t="s">
+      <c r="K1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="O1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2" ht="75.0" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>30</v>
+      <c r="D2" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="E2" s="12">
         <v>4.0</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="H2" s="17"/>
+      <c r="G2" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="19"/>
       <c r="I2" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J2" s="19"/>
+      <c r="J2" s="20"/>
       <c r="K2" s="21" t="s">
         <v>50</v>
       </c>
@@ -7038,16 +7047,16 @@
       </c>
     </row>
     <row r="3" ht="75.0" customHeight="1">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="12">
@@ -7056,7 +7065,7 @@
       <c r="F3" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="18" t="s">
         <v>57</v>
       </c>
       <c r="H3" s="12">
@@ -7065,301 +7074,301 @@
       <c r="I3" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J3" s="19"/>
+      <c r="J3" s="20"/>
       <c r="K3" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" ht="75.0" customHeight="1">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>64</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="E4" s="12">
         <v>4.0</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="17"/>
+      <c r="G4" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="19"/>
       <c r="I4" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J4" s="19"/>
+      <c r="J4" s="20"/>
       <c r="K4" s="21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M4" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N4" s="21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" ht="75.0" customHeight="1">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>73</v>
+      <c r="C5" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="E5" s="12">
         <v>4.0</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" s="17"/>
+        <v>76</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="19"/>
       <c r="I5" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J5" s="19"/>
+      <c r="J5" s="20"/>
       <c r="K5" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L5" s="21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M5" s="21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N5" s="21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" ht="75.0" customHeight="1">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>81</v>
+      <c r="C6" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="E6" s="12">
         <v>3.0</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="G6" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="H6" s="17"/>
+      <c r="G6" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="19"/>
       <c r="I6" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J6" s="19"/>
+      <c r="J6" s="20"/>
       <c r="K6" s="21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M6" s="21" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N6" s="21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O6" s="21" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" ht="75.0" customHeight="1">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>91</v>
+      <c r="C7" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>93</v>
       </c>
       <c r="E7" s="12">
         <v>4.0</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="17"/>
+        <v>94</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="19"/>
       <c r="I7" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J7" s="19"/>
+      <c r="J7" s="20"/>
       <c r="K7" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="M7" s="21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="N7" s="21" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O7" s="21" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" ht="75.0" customHeight="1">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>100</v>
+      <c r="C8" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>102</v>
       </c>
       <c r="E8" s="12">
         <v>3.0</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" s="17"/>
+        <v>103</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="19"/>
       <c r="I8" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J8" s="19"/>
+      <c r="J8" s="20"/>
       <c r="K8" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M8" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N8" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O8" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" ht="75.0" customHeight="1">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>108</v>
+      <c r="C9" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>110</v>
       </c>
       <c r="E9" s="12">
         <v>4.0</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="17"/>
+        <v>111</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" s="19"/>
       <c r="I9" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J9" s="19"/>
+      <c r="J9" s="20"/>
       <c r="K9" s="21" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M9" s="21" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="N9" s="21" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="O9" s="21" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" ht="75.0" customHeight="1">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>116</v>
+      <c r="C10" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>119</v>
       </c>
       <c r="E10" s="12">
         <v>3.0</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="G10" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="G10" s="18" t="s">
         <v>57</v>
       </c>
       <c r="H10" s="12">
@@ -7368,43 +7377,43 @@
       <c r="I10" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J10" s="19"/>
+      <c r="J10" s="20"/>
       <c r="K10" s="21" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M10" s="21" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N10" s="21" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="O10" s="21" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" ht="75.0" customHeight="1">
-      <c r="A11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="A11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>126</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="E11" s="12">
         <v>4.0</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="G11" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" s="18" t="s">
         <v>57</v>
       </c>
       <c r="H11" s="12">
@@ -7413,86 +7422,86 @@
       <c r="I11" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J11" s="19"/>
+      <c r="J11" s="20"/>
       <c r="K11" s="21" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="M11" s="21" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="N11" s="21" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="O11" s="21" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" ht="75.0" customHeight="1">
-      <c r="A12" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>134</v>
+      <c r="A12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>137</v>
       </c>
       <c r="E12" s="12">
         <v>4.0</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="H12" s="17"/>
+        <v>138</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" s="19"/>
       <c r="I12" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J12" s="19"/>
+      <c r="J12" s="20"/>
       <c r="K12" s="21" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="M12" s="21" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="N12" s="21" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="O12" s="21" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" ht="75.0" customHeight="1">
-      <c r="A13" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>142</v>
+      <c r="A13" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>145</v>
       </c>
       <c r="E13" s="12">
         <v>3.0</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="G13" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="G13" s="18" t="s">
         <v>57</v>
       </c>
       <c r="H13" s="12">
@@ -7501,375 +7510,375 @@
       <c r="I13" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J13" s="19"/>
+      <c r="J13" s="20"/>
       <c r="K13" s="21" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M13" s="21" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N13" s="21" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O13" s="21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" ht="75.0" customHeight="1">
-      <c r="A14" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>151</v>
+      <c r="A14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>154</v>
       </c>
       <c r="E14" s="12">
         <v>4.0</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="G14" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="H14" s="17"/>
+        <v>155</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="H14" s="19"/>
       <c r="I14" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J14" s="19"/>
+      <c r="J14" s="20"/>
       <c r="K14" s="21" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M14" s="21" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N14" s="21" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O14" s="21" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" ht="75.0" customHeight="1">
-      <c r="A15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>161</v>
+      <c r="A15" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>164</v>
       </c>
       <c r="E15" s="12">
         <v>4.0</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="H15" s="17"/>
+        <v>165</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="19"/>
       <c r="I15" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J15" s="19"/>
+      <c r="J15" s="20"/>
       <c r="K15" s="21" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="M15" s="21" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="N15" s="21" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="O15" s="21" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" ht="75.0" customHeight="1">
-      <c r="A16" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>169</v>
+      <c r="A16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>172</v>
       </c>
       <c r="E16" s="12">
         <v>4.0</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="H16" s="17"/>
+        <v>173</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="H16" s="19"/>
       <c r="I16" s="12">
         <v>2026.0</v>
       </c>
-      <c r="J16" s="19"/>
+      <c r="J16" s="20"/>
       <c r="K16" s="21" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="M16" s="21" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="N16" s="21" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="O16" s="21" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" ht="75.0" customHeight="1">
-      <c r="A17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>177</v>
+      <c r="A17" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>181</v>
       </c>
       <c r="E17" s="12">
         <v>3.0</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="H17" s="17"/>
+        <v>182</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="H17" s="19"/>
       <c r="I17" s="12">
         <v>2026.0</v>
       </c>
-      <c r="J17" s="19"/>
+      <c r="J17" s="20"/>
       <c r="K17" s="21" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="M17" s="21" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="N17" s="21" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="O17" s="21" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" ht="75.0" customHeight="1">
-      <c r="A18" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>187</v>
+      <c r="A18" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>191</v>
       </c>
       <c r="E18" s="12">
         <v>3.0</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="G18" s="19"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="19"/>
+        <v>192</v>
+      </c>
+      <c r="G18" s="20"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="20"/>
       <c r="K18" s="21" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M18" s="21" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N18" s="21" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="O18" s="21" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" ht="75.0" customHeight="1">
-      <c r="A19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>197</v>
+      <c r="A19" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>200</v>
       </c>
       <c r="E19" s="12">
         <v>4.0</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="H19" s="17"/>
+        <v>201</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="H19" s="19"/>
       <c r="I19" s="12">
         <v>2026.0</v>
       </c>
-      <c r="J19" s="19"/>
+      <c r="J19" s="20"/>
       <c r="K19" s="21" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="M19" s="21" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="N19" s="21" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="O19" s="21" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" ht="75.0" customHeight="1">
-      <c r="A20" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>207</v>
+      <c r="A20" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>209</v>
       </c>
       <c r="E20" s="12">
         <v>3.0</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="H20" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="H20" s="19"/>
       <c r="I20" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J20" s="19"/>
+      <c r="J20" s="20"/>
       <c r="K20" s="21" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="M20" s="21" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N20" s="21" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O20" s="21" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" ht="75.0" customHeight="1">
-      <c r="A21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="D21" s="9" t="s">
+      <c r="A21" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>217</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="E21" s="12">
         <v>4.0</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="H21" s="17"/>
+        <v>219</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H21" s="19"/>
       <c r="I21" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J21" s="19"/>
+      <c r="J21" s="20"/>
       <c r="K21" s="21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M21" s="21" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N21" s="21" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O21" s="21" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" ht="75.0" customHeight="1">
-      <c r="A22" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="C22" s="11" t="s">
+      <c r="A22" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="C22" s="10" t="s">
         <v>226</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>227</v>
       </c>
       <c r="E22" s="12">
         <v>4.0</v>
@@ -7877,14 +7886,14 @@
       <c r="F22" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="H22" s="17"/>
+      <c r="H22" s="19"/>
       <c r="I22" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J22" s="19"/>
+      <c r="J22" s="20"/>
       <c r="K22" s="21" t="s">
         <v>230</v>
       </c>
@@ -7902,16 +7911,16 @@
       </c>
     </row>
     <row r="23" ht="75.0" customHeight="1">
-      <c r="A23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="C23" s="11" t="s">
+      <c r="A23" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="8" t="s">
         <v>236</v>
       </c>
       <c r="E23" s="12">
@@ -7920,10 +7929,10 @@
       <c r="F23" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="G23" s="19"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="19"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="20"/>
       <c r="K23" s="21" t="s">
         <v>238</v>
       </c>
@@ -7941,16 +7950,16 @@
       </c>
     </row>
     <row r="24" ht="75.0" customHeight="1">
-      <c r="A24" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="C24" s="11" t="s">
+      <c r="A24" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="8" t="s">
         <v>244</v>
       </c>
       <c r="E24" s="12">
@@ -7959,12 +7968,12 @@
       <c r="F24" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="20"/>
       <c r="K24" s="21" t="s">
         <v>247</v>
       </c>
@@ -7982,16 +7991,16 @@
       </c>
     </row>
     <row r="25" ht="75.0" customHeight="1">
-      <c r="A25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="C25" s="11" t="s">
+      <c r="A25" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="8" t="s">
         <v>253</v>
       </c>
       <c r="E25" s="12">
@@ -8000,12 +8009,12 @@
       <c r="F25" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="G25" s="16" t="s">
+      <c r="G25" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="20"/>
       <c r="K25" s="21" t="s">
         <v>255</v>
       </c>
@@ -8023,16 +8032,16 @@
       </c>
     </row>
     <row r="26" ht="75.0" customHeight="1">
-      <c r="A26" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="C26" s="11" t="s">
+      <c r="A26" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="8" t="s">
         <v>261</v>
       </c>
       <c r="E26" s="12">
@@ -8041,12 +8050,12 @@
       <c r="F26" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="18" t="s">
         <v>263</v>
       </c>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="20"/>
       <c r="K26" s="21" t="s">
         <v>264</v>
       </c>
@@ -8065,7 +8074,7 @@
     </row>
     <row r="27" ht="75.0" customHeight="1">
       <c r="A27" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B27" s="28" t="s">
         <v>269</v>
@@ -8082,10 +8091,10 @@
       <c r="F27" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="G27" s="19"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="19"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="20"/>
       <c r="K27" s="21" t="s">
         <v>273</v>
       </c>
@@ -8104,7 +8113,7 @@
     </row>
     <row r="28" ht="75.0" customHeight="1">
       <c r="A28" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B28" s="28" t="s">
         <v>269</v>
@@ -8121,7 +8130,7 @@
       <c r="F28" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="G28" s="16" t="s">
+      <c r="G28" s="18" t="s">
         <v>229</v>
       </c>
       <c r="H28" s="12" t="s">
@@ -8130,7 +8139,7 @@
       <c r="I28" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J28" s="19"/>
+      <c r="J28" s="20"/>
       <c r="K28" s="21" t="s">
         <v>282</v>
       </c>
@@ -8149,7 +8158,7 @@
     </row>
     <row r="29" ht="75.0" customHeight="1">
       <c r="A29" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B29" s="28" t="s">
         <v>269</v>
@@ -8160,628 +8169,648 @@
       <c r="D29" s="28" t="s">
         <v>288</v>
       </c>
-      <c r="E29" s="12"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="19"/>
+      <c r="E29" s="12">
+        <v>4.0</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="H29" s="19"/>
+      <c r="I29" s="12">
+        <v>2025.0</v>
+      </c>
+      <c r="J29" s="20"/>
       <c r="K29" s="21" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L29" s="21" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M29" s="21" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N29" s="21" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O29" s="21" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" ht="75.0" customHeight="1">
       <c r="A30" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B30" s="28" t="s">
         <v>269</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E30" s="12">
         <v>4.0</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="G30" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="H30" s="17"/>
+        <v>298</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="H30" s="19"/>
       <c r="I30" s="12">
         <v>2024.0</v>
       </c>
-      <c r="J30" s="19"/>
+      <c r="J30" s="20"/>
       <c r="K30" s="21" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L30" s="21" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M30" s="21" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N30" s="21" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O30" s="21" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="31" ht="75.0" customHeight="1">
       <c r="A31" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E31" s="12">
         <v>4.0</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="G31" s="16" t="s">
-        <v>307</v>
-      </c>
-      <c r="H31" s="17"/>
+        <v>308</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>309</v>
+      </c>
+      <c r="H31" s="19"/>
       <c r="I31" s="12">
         <v>2022.0</v>
       </c>
-      <c r="J31" s="19"/>
+      <c r="J31" s="20"/>
       <c r="K31" s="21" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L31" s="21" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M31" s="21" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N31" s="21" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O31" s="21" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="32" ht="75.0" customHeight="1">
       <c r="A32" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>314</v>
-      </c>
-      <c r="E32" s="12"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="19"/>
+        <v>316</v>
+      </c>
+      <c r="E32" s="12">
+        <v>5.0</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="H32" s="19"/>
+      <c r="I32" s="12">
+        <v>2025.0</v>
+      </c>
+      <c r="J32" s="20"/>
       <c r="K32" s="21" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L32" s="21" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="M32" s="21" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="N32" s="21" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="O32" s="21" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="33" ht="75.0" customHeight="1">
       <c r="A33" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E33" s="12">
         <v>4.0</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="G33" s="19"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="19"/>
+        <v>325</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="H33" s="19"/>
+      <c r="I33" s="12">
+        <v>2025.0</v>
+      </c>
+      <c r="J33" s="20"/>
       <c r="K33" s="21" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="L33" s="21" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M33" s="21" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="N33" s="21" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="O33" s="21" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="34" ht="75.0" customHeight="1">
       <c r="A34" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D34" s="28" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E34" s="12">
         <v>4.0</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="G34" s="16" t="s">
-        <v>332</v>
-      </c>
-      <c r="H34" s="17"/>
+        <v>334</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="H34" s="19"/>
       <c r="I34" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J34" s="19"/>
+      <c r="J34" s="20"/>
       <c r="K34" s="21" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="L34" s="21" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="M34" s="21" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="N34" s="21" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="O34" s="21" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="35" ht="75.0" customHeight="1">
       <c r="A35" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D35" s="28" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E35" s="12">
         <v>3.0</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="G35" s="16" t="s">
-        <v>332</v>
-      </c>
-      <c r="H35" s="17"/>
+        <v>343</v>
+      </c>
+      <c r="G35" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="H35" s="19"/>
       <c r="I35" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J35" s="19"/>
+      <c r="J35" s="20"/>
       <c r="K35" s="21" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="L35" s="21" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="M35" s="21" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="N35" s="21" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="O35" s="21" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="36" ht="75.0" customHeight="1">
       <c r="A36" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E36" s="12">
         <v>4.0</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>348</v>
-      </c>
-      <c r="G36" s="16" t="s">
-        <v>332</v>
-      </c>
-      <c r="H36" s="17"/>
+        <v>351</v>
+      </c>
+      <c r="G36" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="H36" s="19"/>
       <c r="I36" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J36" s="19"/>
+      <c r="J36" s="20"/>
       <c r="K36" s="21" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L36" s="21" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="M36" s="21" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="N36" s="21" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="O36" s="21" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="37" ht="75.0" customHeight="1">
       <c r="A37" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D37" s="28" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E37" s="12" t="s">
         <v>44</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>357</v>
-      </c>
-      <c r="G37" s="19"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="19"/>
+        <v>360</v>
+      </c>
+      <c r="G37" s="20"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="20"/>
       <c r="K37" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L37" s="21" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="M37" s="21" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="N37" s="21" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="O37" s="21" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="38" ht="75.0" customHeight="1">
       <c r="A38" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E38" s="12">
         <v>5.0</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="G38" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="19"/>
+        <v>368</v>
+      </c>
+      <c r="G38" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="20"/>
       <c r="K38" s="21" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="L38" s="21" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="M38" s="21" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="N38" s="21" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="O38" s="21" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="39" ht="75.0" customHeight="1">
       <c r="A39" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E39" s="12">
         <v>3.0</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>374</v>
-      </c>
-      <c r="G39" s="19"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="19"/>
+        <v>377</v>
+      </c>
+      <c r="G39" s="20"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="20"/>
       <c r="K39" s="21" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="L39" s="21" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M39" s="21" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="N39" s="21" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="O39" s="21" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="40" ht="75.0" customHeight="1">
       <c r="A40" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D40" s="28" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E40" s="12">
         <v>4.0</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>383</v>
-      </c>
-      <c r="G40" s="16" t="s">
-        <v>384</v>
-      </c>
-      <c r="H40" s="17"/>
+        <v>386</v>
+      </c>
+      <c r="G40" s="18" t="s">
+        <v>387</v>
+      </c>
+      <c r="H40" s="19"/>
       <c r="I40" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J40" s="19"/>
+      <c r="J40" s="20"/>
       <c r="K40" s="21" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L40" s="21" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M40" s="21" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="N40" s="21" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="O40" s="21" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="41" ht="75.0" customHeight="1">
       <c r="A41" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D41" s="28" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E41" s="12">
         <v>4.0</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="G41" s="16" t="s">
-        <v>393</v>
-      </c>
-      <c r="H41" s="17"/>
+        <v>395</v>
+      </c>
+      <c r="G41" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="H41" s="19"/>
       <c r="I41" s="12">
         <v>2026.0</v>
       </c>
-      <c r="J41" s="19"/>
+      <c r="J41" s="20"/>
       <c r="K41" s="21" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L41" s="21" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="M41" s="21" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="N41" s="21" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="O41" s="21" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="42" ht="75.0" customHeight="1">
       <c r="A42" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D42" s="28" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E42" s="12">
         <v>4.0</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>401</v>
-      </c>
-      <c r="G42" s="16" t="s">
-        <v>393</v>
-      </c>
-      <c r="H42" s="17"/>
+        <v>404</v>
+      </c>
+      <c r="G42" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="H42" s="19"/>
       <c r="I42" s="12">
         <v>2026.0</v>
       </c>
-      <c r="J42" s="19"/>
+      <c r="J42" s="20"/>
       <c r="K42" s="21" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="L42" s="21" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="M42" s="21" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="N42" s="21" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="O42" s="21" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="43" ht="75.0" customHeight="1">
       <c r="A43" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B43" s="28" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E43" s="12">
         <v>4.0</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>410</v>
-      </c>
-      <c r="G43" s="16" t="s">
-        <v>411</v>
-      </c>
-      <c r="H43" s="17"/>
+        <v>413</v>
+      </c>
+      <c r="G43" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="H43" s="19"/>
       <c r="I43" s="12">
         <v>2026.0</v>
       </c>
-      <c r="J43" s="19"/>
+      <c r="J43" s="20"/>
       <c r="K43" s="21" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="L43" s="21" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="M43" s="21" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="N43" s="21" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="O43" s="21" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="44" ht="75.0" customHeight="1">
       <c r="A44" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B44" s="28" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D44" s="28" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E44" s="12">
         <v>4.0</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>419</v>
-      </c>
-      <c r="G44" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="G44" s="18" t="s">
         <v>57</v>
       </c>
       <c r="H44" s="12">
@@ -8790,86 +8819,86 @@
       <c r="I44" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J44" s="19"/>
+      <c r="J44" s="20"/>
       <c r="K44" s="21" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="L44" s="21" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="M44" s="21" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="N44" s="21" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="O44" s="21" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="45" ht="75.0" customHeight="1">
       <c r="A45" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B45" s="28" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D45" s="28" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E45" s="12">
         <v>4.0</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>427</v>
-      </c>
-      <c r="G45" s="16" t="s">
-        <v>332</v>
-      </c>
-      <c r="H45" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="H45" s="19"/>
       <c r="I45" s="12">
         <v>2026.0</v>
       </c>
-      <c r="J45" s="19"/>
+      <c r="J45" s="20"/>
       <c r="K45" s="21" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L45" s="21" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="M45" s="21" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="N45" s="21" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="O45" s="21" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="46" ht="75.0" customHeight="1">
       <c r="A46" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B46" s="28" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D46" s="28" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E46" s="12">
         <v>4.0</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>435</v>
-      </c>
-      <c r="G46" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="G46" s="18" t="s">
         <v>57</v>
       </c>
       <c r="H46" s="12">
@@ -8878,43 +8907,43 @@
       <c r="I46" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J46" s="19"/>
+      <c r="J46" s="20"/>
       <c r="K46" s="21" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L46" s="21" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="M46" s="21" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="N46" s="21" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="O46" s="21" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="47" ht="75.0" customHeight="1">
       <c r="A47" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B47" s="28" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C47" s="29" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D47" s="28" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E47" s="12">
         <v>4.0</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>443</v>
-      </c>
-      <c r="G47" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="G47" s="18" t="s">
         <v>57</v>
       </c>
       <c r="H47" s="12">
@@ -8923,418 +8952,418 @@
       <c r="I47" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J47" s="19"/>
+      <c r="J47" s="20"/>
       <c r="K47" s="21" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="L47" s="21" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="M47" s="21" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="N47" s="21" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="O47" s="21" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="48" ht="75.0" customHeight="1">
       <c r="A48" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B48" s="28" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C48" s="29" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E48" s="12">
         <v>4.0</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>451</v>
-      </c>
-      <c r="G48" s="16" t="s">
-        <v>393</v>
-      </c>
-      <c r="H48" s="17"/>
+        <v>454</v>
+      </c>
+      <c r="G48" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="H48" s="19"/>
       <c r="I48" s="12">
         <v>2026.0</v>
       </c>
-      <c r="J48" s="19"/>
+      <c r="J48" s="20"/>
       <c r="K48" s="21" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="L48" s="21" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="M48" s="21" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="N48" s="21" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="O48" s="21" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="49" ht="75.0" customHeight="1">
       <c r="A49" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B49" s="28" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E49" s="12">
         <v>4.0</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>459</v>
-      </c>
-      <c r="G49" s="16" t="s">
-        <v>393</v>
-      </c>
-      <c r="H49" s="17"/>
+        <v>462</v>
+      </c>
+      <c r="G49" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="H49" s="19"/>
       <c r="I49" s="12">
         <v>2026.0</v>
       </c>
-      <c r="J49" s="19"/>
+      <c r="J49" s="20"/>
       <c r="K49" s="21" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="L49" s="21" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M49" s="21" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="N49" s="21" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="O49" s="21" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="50" ht="75.0" customHeight="1">
       <c r="A50" s="28" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B50" s="28" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D50" s="28" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E50" s="12">
         <v>4.0</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>467</v>
-      </c>
-      <c r="G50" s="16" t="s">
-        <v>393</v>
-      </c>
-      <c r="H50" s="17"/>
+        <v>470</v>
+      </c>
+      <c r="G50" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="H50" s="19"/>
       <c r="I50" s="12">
         <v>2026.0</v>
       </c>
-      <c r="J50" s="19"/>
+      <c r="J50" s="20"/>
       <c r="K50" s="21" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="L50" s="21" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="M50" s="21" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="N50" s="21" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="O50" s="21" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="51" ht="75.0" customHeight="1">
       <c r="A51" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B51" s="30" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C51" s="31" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D51" s="30" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E51" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="17"/>
-      <c r="J51" s="19"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="20"/>
       <c r="K51" s="21" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="L51" s="21" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="M51" s="21" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="N51" s="21" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="O51" s="21" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="52" ht="75.0" customHeight="1">
       <c r="A52" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B52" s="30" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C52" s="31" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D52" s="30" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E52" s="12">
         <v>4.0</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>483</v>
-      </c>
-      <c r="G52" s="16" t="s">
-        <v>411</v>
-      </c>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="19"/>
+        <v>486</v>
+      </c>
+      <c r="G52" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="20"/>
       <c r="K52" s="21" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L52" s="21" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="M52" s="21" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="N52" s="21" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="O52" s="21" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="53" ht="75.0" customHeight="1">
       <c r="A53" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B53" s="30" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C53" s="31" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D53" s="30" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E53" s="12">
         <v>4.0</v>
       </c>
-      <c r="F53" s="19" t="s">
-        <v>491</v>
-      </c>
-      <c r="G53" s="19"/>
+      <c r="F53" s="20" t="s">
+        <v>494</v>
+      </c>
+      <c r="G53" s="20"/>
       <c r="H53" s="12">
         <v>73.0</v>
       </c>
       <c r="I53" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J53" s="19"/>
+      <c r="J53" s="20"/>
       <c r="K53" s="21" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L53" s="21" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="M53" s="21" t="s">
+        <v>497</v>
+      </c>
+      <c r="N53" s="21" t="s">
         <v>494</v>
       </c>
-      <c r="N53" s="21" t="s">
-        <v>491</v>
-      </c>
       <c r="O53" s="21" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="54" ht="75.0" customHeight="1">
       <c r="A54" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B54" s="30" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C54" s="31" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D54" s="30" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>44</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>357</v>
-      </c>
-      <c r="G54" s="19"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="17"/>
-      <c r="J54" s="19"/>
+        <v>360</v>
+      </c>
+      <c r="G54" s="20"/>
+      <c r="H54" s="19"/>
+      <c r="I54" s="19"/>
+      <c r="J54" s="20"/>
       <c r="K54" s="21" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="L54" s="21" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="M54" s="21" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="N54" s="21" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="O54" s="21" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="55" ht="75.0" customHeight="1">
       <c r="A55" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B55" s="30" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C55" s="31" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D55" s="30" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E55" s="12">
         <v>4.0</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>505</v>
-      </c>
-      <c r="G55" s="16" t="s">
-        <v>411</v>
-      </c>
-      <c r="H55" s="17"/>
+        <v>508</v>
+      </c>
+      <c r="G55" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="H55" s="19"/>
       <c r="I55" s="12">
         <v>2026.0</v>
       </c>
-      <c r="J55" s="19"/>
+      <c r="J55" s="20"/>
       <c r="K55" s="21" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="L55" s="21" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="M55" s="21" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="N55" s="21" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="O55" s="21" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="56" ht="75.0" customHeight="1">
       <c r="A56" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B56" s="30" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C56" s="31" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E56" s="12">
         <v>4.0</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>514</v>
-      </c>
-      <c r="G56" s="23" t="s">
-        <v>515</v>
-      </c>
-      <c r="H56" s="17"/>
+        <v>517</v>
+      </c>
+      <c r="G56" s="26" t="s">
+        <v>518</v>
+      </c>
+      <c r="H56" s="19"/>
       <c r="I56" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J56" s="19"/>
+      <c r="J56" s="20"/>
       <c r="K56" s="21" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="L56" s="21" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="M56" s="21" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="N56" s="21" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="O56" s="21" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="57" ht="75.0" customHeight="1">
       <c r="A57" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B57" s="30" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C57" s="31" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D57" s="30" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E57" s="12">
         <v>4.0</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>523</v>
-      </c>
-      <c r="G57" s="16" t="s">
+        <v>526</v>
+      </c>
+      <c r="G57" s="18" t="s">
         <v>57</v>
       </c>
       <c r="H57" s="12">
@@ -9343,211 +9372,211 @@
       <c r="I57" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J57" s="19"/>
+      <c r="J57" s="20"/>
       <c r="K57" s="21" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="L57" s="21" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="M57" s="21" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="N57" s="21" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="O57" s="21" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="58" ht="75.0" customHeight="1">
       <c r="A58" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B58" s="30" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C58" s="31" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D58" s="30" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E58" s="12" t="s">
         <v>44</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>531</v>
-      </c>
-      <c r="G58" s="19"/>
-      <c r="H58" s="17"/>
-      <c r="I58" s="17"/>
-      <c r="J58" s="19"/>
+        <v>534</v>
+      </c>
+      <c r="G58" s="20"/>
+      <c r="H58" s="19"/>
+      <c r="I58" s="19"/>
+      <c r="J58" s="20"/>
       <c r="K58" s="21" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L58" s="21" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="M58" s="21" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="N58" s="21" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="O58" s="21" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="59" ht="75.0" customHeight="1">
       <c r="A59" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B59" s="30" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C59" s="31" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D59" s="30" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E59" s="12">
         <v>4.0</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>539</v>
-      </c>
-      <c r="G59" s="16" t="s">
-        <v>540</v>
-      </c>
-      <c r="H59" s="17"/>
+        <v>542</v>
+      </c>
+      <c r="G59" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="H59" s="19"/>
       <c r="I59" s="12">
         <v>2024.0</v>
       </c>
-      <c r="J59" s="19"/>
+      <c r="J59" s="20"/>
       <c r="K59" s="21" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="L59" s="21" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="M59" s="21" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="N59" s="21" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="O59" s="21" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="60" ht="75.0" customHeight="1">
       <c r="A60" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B60" s="30" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C60" s="31" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D60" s="30" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E60" s="12">
         <v>4.0</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>548</v>
-      </c>
-      <c r="G60" s="23" t="s">
-        <v>549</v>
-      </c>
-      <c r="H60" s="17"/>
+        <v>551</v>
+      </c>
+      <c r="G60" s="26" t="s">
+        <v>552</v>
+      </c>
+      <c r="H60" s="19"/>
       <c r="I60" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J60" s="19"/>
+      <c r="J60" s="20"/>
       <c r="K60" s="21" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L60" s="21" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="M60" s="21" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="N60" s="21" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="O60" s="21" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="61" ht="75.0" customHeight="1">
       <c r="A61" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C61" s="31" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D61" s="30" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E61" s="12">
         <v>4.0</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>557</v>
-      </c>
-      <c r="G61" s="16" t="s">
-        <v>558</v>
-      </c>
-      <c r="H61" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="G61" s="18" t="s">
+        <v>561</v>
+      </c>
+      <c r="H61" s="19"/>
       <c r="I61" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J61" s="19"/>
+      <c r="J61" s="20"/>
       <c r="K61" s="21" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L61" s="21" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="M61" s="21" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="N61" s="21" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="O61" s="21" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="62" ht="75.0" customHeight="1">
       <c r="A62" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B62" s="30" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C62" s="31" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D62" s="30" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="E62" s="12">
         <v>4.0</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>566</v>
-      </c>
-      <c r="G62" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="G62" s="18" t="s">
         <v>57</v>
       </c>
       <c r="H62" s="12">
@@ -9556,432 +9585,432 @@
       <c r="I62" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J62" s="19"/>
+      <c r="J62" s="20"/>
       <c r="K62" s="21" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="L62" s="21" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="M62" s="21" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="N62" s="21" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="O62" s="21" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="63" ht="75.0" customHeight="1">
       <c r="A63" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B63" s="30" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C63" s="31" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D63" s="30" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E63" s="12">
         <v>5.0</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>575</v>
-      </c>
-      <c r="G63" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="H63" s="17"/>
+        <v>578</v>
+      </c>
+      <c r="G63" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H63" s="19"/>
       <c r="I63" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J63" s="19"/>
+      <c r="J63" s="20"/>
       <c r="K63" s="21" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="L63" s="21" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="M63" s="21" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="N63" s="21" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="O63" s="21" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="64" ht="75.0" customHeight="1">
       <c r="A64" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B64" s="30" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C64" s="31" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E64" s="12">
         <v>5.0</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>583</v>
-      </c>
-      <c r="G64" s="16" t="s">
-        <v>584</v>
-      </c>
-      <c r="H64" s="17"/>
+        <v>586</v>
+      </c>
+      <c r="G64" s="18" t="s">
+        <v>587</v>
+      </c>
+      <c r="H64" s="19"/>
       <c r="I64" s="12">
         <v>2026.0</v>
       </c>
-      <c r="J64" s="19"/>
+      <c r="J64" s="20"/>
       <c r="K64" s="21" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="L64" s="21" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="M64" s="21" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="N64" s="21" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="O64" s="21" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
     </row>
     <row r="65" ht="75.0" customHeight="1">
       <c r="A65" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B65" s="30" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C65" s="31" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D65" s="30" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E65" s="12">
         <v>5.0</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>583</v>
-      </c>
-      <c r="G65" s="16" t="s">
-        <v>584</v>
-      </c>
-      <c r="H65" s="17"/>
+        <v>586</v>
+      </c>
+      <c r="G65" s="18" t="s">
+        <v>587</v>
+      </c>
+      <c r="H65" s="19"/>
       <c r="I65" s="12">
         <v>2026.0</v>
       </c>
-      <c r="J65" s="19"/>
+      <c r="J65" s="20"/>
       <c r="K65" s="21" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="L65" s="21" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="M65" s="21" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="N65" s="21" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="O65" s="21" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="66" ht="75.0" customHeight="1">
       <c r="A66" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B66" s="30" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C66" s="31" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D66" s="30" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E66" s="12">
         <v>4.0</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>599</v>
-      </c>
-      <c r="G66" s="16" t="s">
-        <v>600</v>
-      </c>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-      <c r="J66" s="19"/>
+        <v>602</v>
+      </c>
+      <c r="G66" s="18" t="s">
+        <v>603</v>
+      </c>
+      <c r="H66" s="19"/>
+      <c r="I66" s="19"/>
+      <c r="J66" s="20"/>
       <c r="K66" s="21" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="L66" s="21" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="M66" s="21" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="N66" s="21" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="O66" s="21" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="67" ht="75.0" customHeight="1">
       <c r="A67" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B67" s="30" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C67" s="31" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="E67" s="12">
         <v>5.0</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="G67" s="23" t="s">
-        <v>610</v>
-      </c>
-      <c r="H67" s="17"/>
+        <v>612</v>
+      </c>
+      <c r="G67" s="26" t="s">
+        <v>613</v>
+      </c>
+      <c r="H67" s="19"/>
       <c r="I67" s="12">
         <v>2026.0</v>
       </c>
-      <c r="J67" s="19"/>
+      <c r="J67" s="20"/>
       <c r="K67" s="21" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L67" s="21" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="M67" s="21" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="N67" s="21" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="O67" s="21" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="68" ht="75.0" customHeight="1">
       <c r="A68" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B68" s="30" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C68" s="31" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D68" s="30" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="E68" s="12">
         <v>4.0</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>618</v>
-      </c>
-      <c r="G68" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="H68" s="17"/>
+        <v>621</v>
+      </c>
+      <c r="G68" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="H68" s="19"/>
       <c r="I68" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J68" s="19"/>
+      <c r="J68" s="20"/>
       <c r="K68" s="21" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="L68" s="21" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="M68" s="21" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="N68" s="21" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="O68" s="21" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="69" ht="75.0" customHeight="1">
       <c r="A69" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B69" s="30" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C69" s="31" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D69" s="30" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E69" s="12">
         <v>3.0</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>626</v>
-      </c>
-      <c r="G69" s="16" t="s">
-        <v>627</v>
+        <v>629</v>
+      </c>
+      <c r="G69" s="18" t="s">
+        <v>630</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I69" s="12">
         <v>2020.0</v>
       </c>
       <c r="J69" s="13" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="K69" s="21" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="L69" s="21" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="M69" s="21" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="N69" s="21" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="O69" s="21" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
     </row>
     <row r="70" ht="75.0" customHeight="1">
       <c r="A70" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B70" s="30" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C70" s="31" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="E70" s="12">
         <v>3.0</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>637</v>
-      </c>
-      <c r="G70" s="23" t="s">
-        <v>638</v>
+        <v>640</v>
+      </c>
+      <c r="G70" s="26" t="s">
+        <v>641</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I70" s="12">
         <v>2025.0</v>
       </c>
       <c r="J70" s="13" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="K70" s="21" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="L70" s="21" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="M70" s="21" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="N70" s="21" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="O70" s="21" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="71" ht="75.0" customHeight="1">
       <c r="A71" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B71" s="30" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C71" s="31" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="D71" s="30" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="E71" s="12">
         <v>3.0</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>648</v>
-      </c>
-      <c r="G71" s="23" t="s">
-        <v>649</v>
+        <v>651</v>
+      </c>
+      <c r="G71" s="26" t="s">
+        <v>652</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I71" s="12">
         <v>2022.0</v>
       </c>
       <c r="J71" s="13" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="K71" s="21" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="L71" s="21" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="M71" s="21" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="N71" s="21" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="O71" s="21" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="72" ht="75.0" customHeight="1">
       <c r="A72" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B72" s="30" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C72" s="31" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="D72" s="30" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>44</v>
@@ -9989,38 +10018,38 @@
       <c r="F72" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G72" s="19"/>
-      <c r="H72" s="17"/>
-      <c r="I72" s="17"/>
-      <c r="J72" s="19"/>
+      <c r="G72" s="20"/>
+      <c r="H72" s="19"/>
+      <c r="I72" s="19"/>
+      <c r="J72" s="20"/>
       <c r="K72" s="21" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="L72" s="21" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="M72" s="21" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="N72" s="21" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="O72" s="21" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
     </row>
     <row r="73" ht="75.0" customHeight="1">
       <c r="A73" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B73" s="30" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C73" s="31" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D73" s="30" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="E73" s="12" t="s">
         <v>44</v>
@@ -10028,126 +10057,126 @@
       <c r="F73" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G73" s="19"/>
-      <c r="H73" s="17"/>
-      <c r="I73" s="17"/>
-      <c r="J73" s="19"/>
+      <c r="G73" s="20"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="20"/>
       <c r="K73" s="21" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L73" s="21" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="M73" s="21" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="N73" s="21" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="O73" s="21" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="74" ht="75.0" customHeight="1">
       <c r="A74" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B74" s="30" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C74" s="31" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="D74" s="30" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="E74" s="12">
         <v>4.0</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>672</v>
-      </c>
-      <c r="G74" s="16" t="s">
-        <v>673</v>
-      </c>
-      <c r="H74" s="17"/>
+        <v>675</v>
+      </c>
+      <c r="G74" s="18" t="s">
+        <v>676</v>
+      </c>
+      <c r="H74" s="19"/>
       <c r="I74" s="12">
         <v>2020.0</v>
       </c>
-      <c r="J74" s="19"/>
+      <c r="J74" s="20"/>
       <c r="K74" s="21" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="L74" s="21" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="M74" s="21" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="N74" s="21" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="O74" s="21" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
     </row>
     <row r="75" ht="75.0" customHeight="1">
       <c r="A75" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B75" s="30" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C75" s="31" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="D75" s="30" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="E75" s="12">
         <v>4.0</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>681</v>
-      </c>
-      <c r="G75" s="23" t="s">
-        <v>682</v>
+        <v>684</v>
+      </c>
+      <c r="G75" s="26" t="s">
+        <v>685</v>
       </c>
       <c r="H75" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I75" s="12">
         <v>2022.0</v>
       </c>
-      <c r="J75" s="19"/>
+      <c r="J75" s="20"/>
       <c r="K75" s="21" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="L75" s="21" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="M75" s="21" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="N75" s="21" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="O75" s="21" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="76" ht="75.0" customHeight="1">
       <c r="A76" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B76" s="30" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C76" s="31" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D76" s="30" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>44</v>
@@ -10155,47 +10184,47 @@
       <c r="F76" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G76" s="19"/>
-      <c r="H76" s="17"/>
-      <c r="I76" s="17"/>
-      <c r="J76" s="19"/>
+      <c r="G76" s="20"/>
+      <c r="H76" s="19"/>
+      <c r="I76" s="19"/>
+      <c r="J76" s="20"/>
       <c r="K76" s="21" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="L76" s="21" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="M76" s="21" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="N76" s="21" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="O76" s="21" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="77" ht="75.0" customHeight="1">
       <c r="A77" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B77" s="30" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C77" s="31" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="D77" s="30" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="E77" s="12">
         <v>4.0</v>
       </c>
       <c r="F77" s="13" t="s">
-        <v>697</v>
-      </c>
-      <c r="G77" s="23" t="s">
-        <v>698</v>
+        <v>700</v>
+      </c>
+      <c r="G77" s="26" t="s">
+        <v>701</v>
       </c>
       <c r="H77" s="12">
         <v>24.0</v>
@@ -10203,659 +10232,659 @@
       <c r="I77" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J77" s="19"/>
+      <c r="J77" s="20"/>
       <c r="K77" s="21" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="L77" s="21" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="M77" s="21" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="N77" s="21" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="O77" s="21" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="78" ht="75.0" customHeight="1">
       <c r="A78" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B78" s="30" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C78" s="31" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="D78" s="30" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="E78" s="12" t="s">
         <v>44</v>
       </c>
       <c r="F78" s="13" t="s">
-        <v>706</v>
-      </c>
-      <c r="G78" s="19"/>
-      <c r="H78" s="17"/>
-      <c r="I78" s="17"/>
-      <c r="J78" s="19"/>
+        <v>709</v>
+      </c>
+      <c r="G78" s="20"/>
+      <c r="H78" s="19"/>
+      <c r="I78" s="19"/>
+      <c r="J78" s="20"/>
       <c r="K78" s="21" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="L78" s="21" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="M78" s="21" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="N78" s="21" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="O78" s="21" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
     </row>
     <row r="79" ht="75.0" customHeight="1">
       <c r="A79" s="30" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C79" s="31" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="E79" s="12">
         <v>5.0</v>
       </c>
       <c r="F79" s="13" t="s">
-        <v>714</v>
-      </c>
-      <c r="G79" s="23" t="s">
-        <v>715</v>
-      </c>
-      <c r="H79" s="17"/>
+        <v>717</v>
+      </c>
+      <c r="G79" s="26" t="s">
+        <v>718</v>
+      </c>
+      <c r="H79" s="19"/>
       <c r="I79" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J79" s="19"/>
+      <c r="J79" s="20"/>
       <c r="K79" s="21" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="L79" s="21" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="M79" s="21" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="N79" s="21" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="O79" s="21" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
     </row>
     <row r="80" ht="75.0" customHeight="1">
       <c r="A80" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B80" s="32" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C80" s="33" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="D80" s="32" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="E80" s="12">
         <v>4.0</v>
       </c>
       <c r="F80" s="13" t="s">
-        <v>724</v>
-      </c>
-      <c r="G80" s="23" t="s">
-        <v>725</v>
+        <v>727</v>
+      </c>
+      <c r="G80" s="26" t="s">
+        <v>728</v>
       </c>
       <c r="H80" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I80" s="12">
         <v>2024.0</v>
       </c>
-      <c r="J80" s="19"/>
+      <c r="J80" s="20"/>
       <c r="K80" s="21" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="L80" s="21" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="M80" s="21" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="N80" s="21" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="O80" s="21" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
     <row r="81" ht="75.0" customHeight="1">
       <c r="A81" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B81" s="32" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C81" s="33" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="D81" s="32" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="E81" s="12">
         <v>4.0</v>
       </c>
       <c r="F81" s="13" t="s">
-        <v>733</v>
-      </c>
-      <c r="G81" s="23" t="s">
+        <v>736</v>
+      </c>
+      <c r="G81" s="26" t="s">
         <v>57</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="I81" s="12">
         <v>2025.0</v>
       </c>
       <c r="J81" s="13"/>
       <c r="K81" s="21" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="L81" s="21" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="M81" s="21" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="N81" s="21" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="O81" s="21" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="82" ht="75.0" customHeight="1">
       <c r="A82" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B82" s="32" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C82" s="33" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="D82" s="32" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="E82" s="12">
         <v>4.0</v>
       </c>
       <c r="F82" s="13" t="s">
-        <v>742</v>
-      </c>
-      <c r="G82" s="23" t="s">
-        <v>743</v>
+        <v>745</v>
+      </c>
+      <c r="G82" s="26" t="s">
+        <v>746</v>
       </c>
       <c r="H82" s="12" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="I82" s="12">
         <v>2025.0</v>
       </c>
       <c r="J82" s="13"/>
       <c r="K82" s="21" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="L82" s="21" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="M82" s="21" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="N82" s="21" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="O82" s="21" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
     </row>
     <row r="83" ht="75.0" customHeight="1">
       <c r="A83" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B83" s="32" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C83" s="33" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="D83" s="32" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E83" s="12">
         <v>4.0</v>
       </c>
       <c r="F83" s="13" t="s">
-        <v>752</v>
-      </c>
-      <c r="G83" s="16" t="s">
-        <v>753</v>
+        <v>755</v>
+      </c>
+      <c r="G83" s="18" t="s">
+        <v>756</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I83" s="12">
         <v>2022.0</v>
       </c>
       <c r="J83" s="13"/>
       <c r="K83" s="21" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="L83" s="21" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="M83" s="21" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="N83" s="21" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="O83" s="21" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
     </row>
     <row r="84" ht="75.0" customHeight="1">
       <c r="A84" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B84" s="32" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C84" s="33" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="D84" s="32" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="E84" s="12">
         <v>4.0</v>
       </c>
       <c r="F84" s="13" t="s">
-        <v>762</v>
-      </c>
-      <c r="G84" s="23" t="s">
-        <v>763</v>
+        <v>765</v>
+      </c>
+      <c r="G84" s="26" t="s">
+        <v>766</v>
       </c>
       <c r="H84" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I84" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J84" s="19"/>
+      <c r="J84" s="20"/>
       <c r="K84" s="21" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="L84" s="21" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="M84" s="21" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="N84" s="21" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="O84" s="21" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
     </row>
     <row r="85" ht="75.0" customHeight="1">
       <c r="A85" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B85" s="32" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C85" s="33" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D85" s="32" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="E85" s="12">
         <v>3.0</v>
       </c>
       <c r="F85" s="13" t="s">
-        <v>771</v>
-      </c>
-      <c r="G85" s="16" t="s">
-        <v>772</v>
+        <v>774</v>
+      </c>
+      <c r="G85" s="18" t="s">
+        <v>775</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I85" s="12">
         <v>2025.0</v>
       </c>
       <c r="J85" s="13"/>
       <c r="K85" s="21" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="L85" s="21" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="M85" s="21" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="N85" s="21" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="O85" s="21" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
     </row>
     <row r="86" ht="75.0" customHeight="1">
       <c r="A86" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B86" s="32" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C86" s="33" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="D86" s="32" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="E86" s="12">
         <v>3.0</v>
       </c>
       <c r="F86" s="13" t="s">
-        <v>780</v>
-      </c>
-      <c r="G86" s="23" t="s">
-        <v>781</v>
+        <v>783</v>
+      </c>
+      <c r="G86" s="26" t="s">
+        <v>784</v>
       </c>
       <c r="H86" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I86" s="12">
         <v>2023.0</v>
       </c>
       <c r="J86" s="13"/>
       <c r="K86" s="21" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="L86" s="21" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="M86" s="21" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="N86" s="21" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="O86" s="21" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
     </row>
     <row r="87" ht="75.0" customHeight="1">
       <c r="A87" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B87" s="32" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C87" s="33" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="D87" s="32" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="E87" s="12">
         <v>4.0</v>
       </c>
       <c r="F87" s="13" t="s">
-        <v>789</v>
-      </c>
-      <c r="G87" s="23" t="s">
-        <v>790</v>
+        <v>792</v>
+      </c>
+      <c r="G87" s="26" t="s">
+        <v>793</v>
       </c>
       <c r="H87" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I87" s="12">
         <v>2025.0</v>
       </c>
       <c r="J87" s="13" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="K87" s="21" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="L87" s="21" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="M87" s="21" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="N87" s="21" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="O87" s="21" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="88" ht="75.0" customHeight="1">
       <c r="A88" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B88" s="32" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C88" s="33" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D88" s="32" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="E88" s="12">
         <v>5.0</v>
       </c>
       <c r="F88" s="13" t="s">
-        <v>799</v>
-      </c>
-      <c r="G88" s="23" t="s">
-        <v>800</v>
+        <v>802</v>
+      </c>
+      <c r="G88" s="26" t="s">
+        <v>803</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I88" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J88" s="19"/>
+      <c r="J88" s="20"/>
       <c r="K88" s="21" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="L88" s="21" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="M88" s="21" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="N88" s="21" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="O88" s="21" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
     </row>
     <row r="89" ht="75.0" customHeight="1">
       <c r="A89" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B89" s="32" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C89" s="33" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D89" s="32" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="E89" s="12">
         <v>5.0</v>
       </c>
       <c r="F89" s="13" t="s">
-        <v>808</v>
-      </c>
-      <c r="G89" s="23" t="s">
-        <v>809</v>
+        <v>811</v>
+      </c>
+      <c r="G89" s="26" t="s">
+        <v>812</v>
       </c>
       <c r="H89" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I89" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J89" s="19"/>
+      <c r="J89" s="20"/>
       <c r="K89" s="21" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="L89" s="21" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="M89" s="21" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="N89" s="21" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="O89" s="21" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
     </row>
     <row r="90" ht="75.0" customHeight="1">
       <c r="A90" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B90" s="32" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C90" s="33" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="D90" s="32" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="E90" s="12">
         <v>3.0</v>
       </c>
       <c r="F90" s="13" t="s">
-        <v>818</v>
-      </c>
-      <c r="G90" s="16" t="s">
-        <v>819</v>
+        <v>821</v>
+      </c>
+      <c r="G90" s="18" t="s">
+        <v>822</v>
       </c>
       <c r="H90" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I90" s="12">
         <v>2018.0</v>
       </c>
       <c r="J90" s="13"/>
       <c r="K90" s="21" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="L90" s="21" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="M90" s="21" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="N90" s="21" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="O90" s="21" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="91" ht="75.0" customHeight="1">
       <c r="A91" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B91" s="32" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C91" s="33" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D91" s="32" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E91" s="12">
         <v>3.0</v>
       </c>
       <c r="F91" s="13" t="s">
-        <v>827</v>
-      </c>
-      <c r="G91" s="16" t="s">
-        <v>627</v>
+        <v>830</v>
+      </c>
+      <c r="G91" s="18" t="s">
+        <v>630</v>
       </c>
       <c r="H91" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I91" s="12">
         <v>2020.0</v>
       </c>
       <c r="J91" s="13"/>
       <c r="K91" s="21" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="L91" s="21" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="M91" s="21" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="N91" s="21" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="O91" s="21" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
     </row>
     <row r="92" ht="75.0" customHeight="1">
       <c r="A92" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B92" s="32" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C92" s="33" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D92" s="32" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="E92" s="12" t="s">
         <v>44</v>
@@ -10863,128 +10892,128 @@
       <c r="F92" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G92" s="19"/>
-      <c r="H92" s="17"/>
-      <c r="I92" s="17"/>
-      <c r="J92" s="19"/>
+      <c r="G92" s="20"/>
+      <c r="H92" s="19"/>
+      <c r="I92" s="19"/>
+      <c r="J92" s="20"/>
       <c r="K92" s="21" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="L92" s="21" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="M92" s="21" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="N92" s="21" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="O92" s="21" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
     </row>
     <row r="93" ht="75.0" customHeight="1">
       <c r="A93" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B93" s="32" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C93" s="33" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="D93" s="32" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="E93" s="12">
         <v>4.0</v>
       </c>
       <c r="F93" s="13" t="s">
-        <v>842</v>
-      </c>
-      <c r="G93" s="16" t="s">
-        <v>627</v>
+        <v>845</v>
+      </c>
+      <c r="G93" s="18" t="s">
+        <v>630</v>
       </c>
       <c r="H93" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I93" s="12">
         <v>2020.0</v>
       </c>
       <c r="J93" s="13"/>
       <c r="K93" s="21" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="L93" s="21" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="M93" s="21" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="N93" s="21" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="O93" s="21" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
     </row>
     <row r="94" ht="75.0" customHeight="1">
       <c r="A94" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B94" s="32" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C94" s="33" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="D94" s="32" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="E94" s="12">
         <v>4.0</v>
       </c>
       <c r="F94" s="13" t="s">
-        <v>851</v>
-      </c>
-      <c r="G94" s="23" t="s">
-        <v>852</v>
+        <v>854</v>
+      </c>
+      <c r="G94" s="26" t="s">
+        <v>855</v>
       </c>
       <c r="H94" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I94" s="12">
         <v>2022.0</v>
       </c>
-      <c r="J94" s="19"/>
+      <c r="J94" s="20"/>
       <c r="K94" s="21" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="L94" s="21" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="M94" s="21" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="N94" s="21" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="O94" s="21" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
     </row>
     <row r="95" ht="75.0" customHeight="1">
       <c r="A95" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B95" s="32" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C95" s="33" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="D95" s="32" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="E95" s="12" t="s">
         <v>44</v>
@@ -10992,38 +11021,38 @@
       <c r="F95" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G95" s="19"/>
-      <c r="H95" s="17"/>
-      <c r="I95" s="17"/>
-      <c r="J95" s="19"/>
+      <c r="G95" s="20"/>
+      <c r="H95" s="19"/>
+      <c r="I95" s="19"/>
+      <c r="J95" s="20"/>
       <c r="K95" s="21" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="L95" s="21" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="M95" s="21" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="N95" s="21" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="O95" s="21" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
     </row>
     <row r="96" ht="75.0" customHeight="1">
       <c r="A96" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B96" s="32" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C96" s="33" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="D96" s="32" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="E96" s="12" t="s">
         <v>44</v>
@@ -11031,128 +11060,128 @@
       <c r="F96" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G96" s="19"/>
-      <c r="H96" s="17"/>
-      <c r="I96" s="17"/>
+      <c r="G96" s="20"/>
+      <c r="H96" s="19"/>
+      <c r="I96" s="19"/>
       <c r="J96" s="13"/>
       <c r="K96" s="21" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="L96" s="21" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="M96" s="21" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="N96" s="21" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="O96" s="21" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
     </row>
     <row r="97" ht="75.0" customHeight="1">
       <c r="A97" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B97" s="32" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C97" s="33" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="D97" s="32" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="E97" s="12">
         <v>4.0</v>
       </c>
       <c r="F97" s="13" t="s">
-        <v>874</v>
-      </c>
-      <c r="G97" s="23" t="s">
-        <v>875</v>
+        <v>877</v>
+      </c>
+      <c r="G97" s="26" t="s">
+        <v>878</v>
       </c>
       <c r="H97" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I97" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J97" s="19"/>
+      <c r="J97" s="20"/>
       <c r="K97" s="21" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="L97" s="21" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="M97" s="21" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="N97" s="21" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="O97" s="21" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
     </row>
     <row r="98" ht="75.0" customHeight="1">
       <c r="A98" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B98" s="32" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C98" s="33" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="D98" s="32" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="E98" s="12">
         <v>4.0</v>
       </c>
       <c r="F98" s="13" t="s">
-        <v>883</v>
-      </c>
-      <c r="G98" s="23" t="s">
-        <v>884</v>
+        <v>886</v>
+      </c>
+      <c r="G98" s="26" t="s">
+        <v>887</v>
       </c>
       <c r="H98" s="12" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="I98" s="12">
         <v>2026.0</v>
       </c>
       <c r="J98" s="13"/>
       <c r="K98" s="21" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="L98" s="21" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="M98" s="21" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="N98" s="21" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="O98" s="21" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
     </row>
     <row r="99" ht="75.0" customHeight="1">
       <c r="A99" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B99" s="32" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C99" s="33" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="D99" s="32" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="E99" s="12" t="s">
         <v>44</v>
@@ -11160,263 +11189,263 @@
       <c r="F99" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G99" s="19"/>
-      <c r="H99" s="17"/>
-      <c r="I99" s="17"/>
-      <c r="J99" s="19"/>
+      <c r="G99" s="20"/>
+      <c r="H99" s="19"/>
+      <c r="I99" s="19"/>
+      <c r="J99" s="20"/>
       <c r="K99" s="21" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="L99" s="21" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="M99" s="21" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="N99" s="21" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="O99" s="21" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
     </row>
     <row r="100" ht="75.0" customHeight="1">
       <c r="A100" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B100" s="32" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C100" s="33" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="D100" s="32" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="E100" s="12">
         <v>5.0</v>
       </c>
       <c r="F100" s="13" t="s">
-        <v>900</v>
-      </c>
-      <c r="G100" s="23" t="s">
-        <v>901</v>
+        <v>903</v>
+      </c>
+      <c r="G100" s="26" t="s">
+        <v>904</v>
       </c>
       <c r="H100" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I100" s="12">
         <v>2026.0</v>
       </c>
-      <c r="J100" s="19"/>
+      <c r="J100" s="20"/>
       <c r="K100" s="21" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="L100" s="21" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="M100" s="21" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="N100" s="21" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="O100" s="21" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
     </row>
     <row r="101" ht="75.0" customHeight="1">
       <c r="A101" s="32" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="B101" s="32" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C101" s="33" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D101" s="32" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="E101" s="12">
         <v>4.0</v>
       </c>
       <c r="F101" s="13" t="s">
-        <v>909</v>
-      </c>
-      <c r="G101" s="23" t="s">
-        <v>910</v>
+        <v>912</v>
+      </c>
+      <c r="G101" s="26" t="s">
+        <v>913</v>
       </c>
       <c r="H101" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I101" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J101" s="19"/>
+      <c r="J101" s="20"/>
       <c r="K101" s="21" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="L101" s="21" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="M101" s="21" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="N101" s="21" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="O101" s="21" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="102" ht="75.0" customHeight="1">
-      <c r="A102" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B102" s="19" t="s">
-        <v>916</v>
+      <c r="A102" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B102" s="20" t="s">
+        <v>919</v>
       </c>
       <c r="C102" s="34" t="s">
-        <v>917</v>
-      </c>
-      <c r="D102" s="19" t="s">
-        <v>918</v>
+        <v>920</v>
+      </c>
+      <c r="D102" s="20" t="s">
+        <v>921</v>
       </c>
       <c r="E102" s="12">
         <v>4.0</v>
       </c>
       <c r="F102" s="13" t="s">
-        <v>919</v>
-      </c>
-      <c r="G102" s="23" t="s">
-        <v>920</v>
+        <v>922</v>
+      </c>
+      <c r="G102" s="26" t="s">
+        <v>923</v>
       </c>
       <c r="H102" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I102" s="12">
         <v>2022.0</v>
       </c>
-      <c r="J102" s="19"/>
+      <c r="J102" s="20"/>
       <c r="K102" s="21" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="L102" s="21" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="M102" s="21" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="N102" s="21" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="O102" s="21" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
     </row>
     <row r="103" ht="75.0" customHeight="1">
-      <c r="A103" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B103" s="19" t="s">
-        <v>916</v>
+      <c r="A103" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B103" s="20" t="s">
+        <v>919</v>
       </c>
       <c r="C103" s="34" t="s">
-        <v>926</v>
-      </c>
-      <c r="D103" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
+      </c>
+      <c r="D103" s="20" t="s">
+        <v>930</v>
       </c>
       <c r="E103" s="12">
         <v>3.0</v>
       </c>
       <c r="F103" s="13" t="s">
-        <v>928</v>
-      </c>
-      <c r="G103" s="16" t="s">
-        <v>929</v>
+        <v>931</v>
+      </c>
+      <c r="G103" s="18" t="s">
+        <v>932</v>
       </c>
       <c r="H103" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I103" s="12">
         <v>2023.0</v>
       </c>
-      <c r="J103" s="19"/>
+      <c r="J103" s="20"/>
       <c r="K103" s="21" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="L103" s="21" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="M103" s="21" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="N103" s="21" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="O103" s="21" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
     </row>
     <row r="104" ht="75.0" customHeight="1">
-      <c r="A104" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B104" s="19" t="s">
-        <v>916</v>
+      <c r="A104" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B104" s="20" t="s">
+        <v>919</v>
       </c>
       <c r="C104" s="34" t="s">
-        <v>935</v>
-      </c>
-      <c r="D104" s="19" t="s">
-        <v>936</v>
+        <v>938</v>
+      </c>
+      <c r="D104" s="20" t="s">
+        <v>939</v>
       </c>
       <c r="E104" s="12">
         <v>4.0</v>
       </c>
       <c r="F104" s="13" t="s">
-        <v>937</v>
-      </c>
-      <c r="G104" s="23" t="s">
-        <v>938</v>
+        <v>940</v>
+      </c>
+      <c r="G104" s="26" t="s">
+        <v>941</v>
       </c>
       <c r="H104" s="12" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="I104" s="12">
         <v>2025.0</v>
       </c>
       <c r="J104" s="13"/>
       <c r="K104" s="21" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="L104" s="21" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="M104" s="21" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="N104" s="21" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="O104" s="21" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
     </row>
     <row r="105" ht="75.0" customHeight="1">
-      <c r="A105" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B105" s="19" t="s">
-        <v>916</v>
+      <c r="A105" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B105" s="20" t="s">
+        <v>919</v>
       </c>
       <c r="C105" s="34" t="s">
-        <v>944</v>
-      </c>
-      <c r="D105" s="19" t="s">
-        <v>945</v>
+        <v>947</v>
+      </c>
+      <c r="D105" s="20" t="s">
+        <v>948</v>
       </c>
       <c r="E105" s="12" t="s">
         <v>44</v>
@@ -11424,85 +11453,85 @@
       <c r="F105" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G105" s="19"/>
-      <c r="H105" s="17"/>
-      <c r="I105" s="17"/>
-      <c r="J105" s="19"/>
+      <c r="G105" s="20"/>
+      <c r="H105" s="19"/>
+      <c r="I105" s="19"/>
+      <c r="J105" s="20"/>
       <c r="K105" s="21" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="L105" s="21" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="M105" s="21" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="N105" s="21" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="O105" s="21" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
     </row>
     <row r="106" ht="75.0" customHeight="1">
-      <c r="A106" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B106" s="19" t="s">
-        <v>916</v>
+      <c r="A106" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B106" s="20" t="s">
+        <v>919</v>
       </c>
       <c r="C106" s="34" t="s">
-        <v>951</v>
-      </c>
-      <c r="D106" s="19" t="s">
-        <v>952</v>
+        <v>954</v>
+      </c>
+      <c r="D106" s="20" t="s">
+        <v>955</v>
       </c>
       <c r="E106" s="12">
         <v>3.0</v>
       </c>
       <c r="F106" s="13" t="s">
-        <v>953</v>
-      </c>
-      <c r="G106" s="23" t="s">
-        <v>954</v>
+        <v>956</v>
+      </c>
+      <c r="G106" s="26" t="s">
+        <v>957</v>
       </c>
       <c r="H106" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I106" s="12">
         <v>2025.0</v>
       </c>
       <c r="J106" s="13" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="K106" s="21" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="L106" s="21" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="M106" s="21" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="N106" s="21" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="O106" s="21" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
     </row>
     <row r="107" ht="75.0" customHeight="1">
-      <c r="A107" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B107" s="19" t="s">
-        <v>916</v>
+      <c r="A107" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B107" s="20" t="s">
+        <v>919</v>
       </c>
       <c r="C107" s="34" t="s">
-        <v>961</v>
-      </c>
-      <c r="D107" s="19" t="s">
-        <v>962</v>
+        <v>964</v>
+      </c>
+      <c r="D107" s="20" t="s">
+        <v>965</v>
       </c>
       <c r="E107" s="12" t="s">
         <v>44</v>
@@ -11510,319 +11539,319 @@
       <c r="F107" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G107" s="19"/>
-      <c r="H107" s="17"/>
-      <c r="I107" s="17"/>
+      <c r="G107" s="20"/>
+      <c r="H107" s="19"/>
+      <c r="I107" s="19"/>
       <c r="J107" s="13" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="K107" s="21" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="L107" s="21" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="M107" s="21" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="N107" s="21" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="O107" s="21" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
     </row>
     <row r="108" ht="75.0" customHeight="1">
-      <c r="A108" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B108" s="19" t="s">
-        <v>969</v>
+      <c r="A108" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B108" s="20" t="s">
+        <v>972</v>
       </c>
       <c r="C108" s="34" t="s">
-        <v>970</v>
-      </c>
-      <c r="D108" s="19" t="s">
-        <v>971</v>
+        <v>973</v>
+      </c>
+      <c r="D108" s="20" t="s">
+        <v>974</v>
       </c>
       <c r="E108" s="12">
         <v>3.0</v>
       </c>
       <c r="F108" s="13" t="s">
-        <v>972</v>
-      </c>
-      <c r="G108" s="23" t="s">
-        <v>973</v>
+        <v>975</v>
+      </c>
+      <c r="G108" s="26" t="s">
+        <v>976</v>
       </c>
       <c r="H108" s="12" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="I108" s="12">
         <v>2025.0</v>
       </c>
       <c r="J108" s="13"/>
       <c r="K108" s="21" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="L108" s="21" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="M108" s="21" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="N108" s="21" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="O108" s="21" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
     </row>
     <row r="109" ht="75.0" customHeight="1">
-      <c r="A109" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B109" s="19" t="s">
-        <v>969</v>
+      <c r="A109" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B109" s="20" t="s">
+        <v>972</v>
       </c>
       <c r="C109" s="34" t="s">
-        <v>979</v>
-      </c>
-      <c r="D109" s="19" t="s">
-        <v>980</v>
+        <v>982</v>
+      </c>
+      <c r="D109" s="20" t="s">
+        <v>983</v>
       </c>
       <c r="E109" s="12">
         <v>3.0</v>
       </c>
       <c r="F109" s="13" t="s">
-        <v>981</v>
-      </c>
-      <c r="G109" s="16" t="s">
-        <v>929</v>
+        <v>984</v>
+      </c>
+      <c r="G109" s="18" t="s">
+        <v>932</v>
       </c>
       <c r="H109" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I109" s="12">
         <v>2023.0</v>
       </c>
-      <c r="J109" s="19"/>
+      <c r="J109" s="20"/>
       <c r="K109" s="21" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="L109" s="21" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="M109" s="21" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="N109" s="21" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="O109" s="21" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
     </row>
     <row r="110" ht="75.0" customHeight="1">
-      <c r="A110" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B110" s="19" t="s">
-        <v>969</v>
+      <c r="A110" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B110" s="20" t="s">
+        <v>972</v>
       </c>
       <c r="C110" s="34" t="s">
-        <v>987</v>
-      </c>
-      <c r="D110" s="19" t="s">
-        <v>988</v>
+        <v>990</v>
+      </c>
+      <c r="D110" s="20" t="s">
+        <v>991</v>
       </c>
       <c r="E110" s="12">
         <v>3.0</v>
       </c>
       <c r="F110" s="13" t="s">
-        <v>989</v>
-      </c>
-      <c r="G110" s="23" t="s">
-        <v>990</v>
+        <v>992</v>
+      </c>
+      <c r="G110" s="26" t="s">
+        <v>993</v>
       </c>
       <c r="H110" s="12" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="I110" s="12">
         <v>2025.0</v>
       </c>
       <c r="J110" s="13"/>
       <c r="K110" s="21" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="L110" s="21" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="M110" s="21" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="N110" s="21" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="O110" s="21" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
     </row>
     <row r="111" ht="75.0" customHeight="1">
-      <c r="A111" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B111" s="19" t="s">
-        <v>969</v>
+      <c r="A111" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B111" s="20" t="s">
+        <v>972</v>
       </c>
       <c r="C111" s="34" t="s">
-        <v>997</v>
-      </c>
-      <c r="D111" s="19" t="s">
-        <v>998</v>
+        <v>1000</v>
+      </c>
+      <c r="D111" s="20" t="s">
+        <v>1001</v>
       </c>
       <c r="E111" s="12">
         <v>4.0</v>
       </c>
       <c r="F111" s="13" t="s">
-        <v>999</v>
-      </c>
-      <c r="G111" s="23" t="s">
-        <v>1000</v>
+        <v>1002</v>
+      </c>
+      <c r="G111" s="26" t="s">
+        <v>1003</v>
       </c>
       <c r="H111" s="12" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="I111" s="12">
         <v>2023.0</v>
       </c>
       <c r="J111" s="13"/>
       <c r="K111" s="21" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="L111" s="21" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="M111" s="21" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="N111" s="21" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="O111" s="21" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="112" ht="75.0" customHeight="1">
-      <c r="A112" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B112" s="19" t="s">
-        <v>969</v>
+      <c r="A112" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B112" s="20" t="s">
+        <v>972</v>
       </c>
       <c r="C112" s="34" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D112" s="19" t="s">
-        <v>1007</v>
+        <v>1009</v>
+      </c>
+      <c r="D112" s="20" t="s">
+        <v>1010</v>
       </c>
       <c r="E112" s="12">
         <v>3.0</v>
       </c>
       <c r="F112" s="13" t="s">
-        <v>1008</v>
-      </c>
-      <c r="G112" s="16" t="s">
-        <v>627</v>
+        <v>1011</v>
+      </c>
+      <c r="G112" s="18" t="s">
+        <v>630</v>
       </c>
       <c r="H112" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I112" s="12">
         <v>2020.0</v>
       </c>
       <c r="J112" s="13"/>
       <c r="K112" s="21" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="L112" s="21" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="M112" s="21" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="N112" s="21" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="O112" s="21" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="113" ht="75.0" customHeight="1">
-      <c r="A113" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B113" s="19" t="s">
-        <v>969</v>
+      <c r="A113" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B113" s="20" t="s">
+        <v>972</v>
       </c>
       <c r="C113" s="34" t="s">
-        <v>1014</v>
-      </c>
-      <c r="D113" s="19" t="s">
-        <v>1015</v>
+        <v>1017</v>
+      </c>
+      <c r="D113" s="20" t="s">
+        <v>1018</v>
       </c>
       <c r="E113" s="12">
         <v>3.0</v>
       </c>
       <c r="F113" s="13" t="s">
-        <v>1016</v>
-      </c>
-      <c r="G113" s="16" t="s">
-        <v>929</v>
+        <v>1019</v>
+      </c>
+      <c r="G113" s="18" t="s">
+        <v>932</v>
       </c>
       <c r="H113" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I113" s="12">
         <v>2023.0</v>
       </c>
-      <c r="J113" s="19"/>
+      <c r="J113" s="20"/>
       <c r="K113" s="21" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="L113" s="21" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="M113" s="21" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="N113" s="21" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="O113" s="21" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="114" ht="75.0" customHeight="1">
-      <c r="A114" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B114" s="19" t="s">
-        <v>969</v>
+      <c r="A114" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B114" s="20" t="s">
+        <v>972</v>
       </c>
       <c r="C114" s="34" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D114" s="19" t="s">
-        <v>1023</v>
+        <v>1025</v>
+      </c>
+      <c r="D114" s="20" t="s">
+        <v>1026</v>
       </c>
       <c r="E114" s="12">
         <v>3.0</v>
       </c>
       <c r="F114" s="13" t="s">
-        <v>1024</v>
-      </c>
-      <c r="G114" s="23" t="s">
-        <v>1025</v>
+        <v>1027</v>
+      </c>
+      <c r="G114" s="26" t="s">
+        <v>1028</v>
       </c>
       <c r="H114" s="12">
         <v>18.0</v>
@@ -11832,213 +11861,213 @@
       </c>
       <c r="J114" s="13"/>
       <c r="K114" s="21" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="L114" s="21" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="M114" s="21" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="N114" s="21" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="O114" s="21" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="115" ht="75.0" customHeight="1">
-      <c r="A115" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B115" s="19" t="s">
-        <v>969</v>
+      <c r="A115" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B115" s="20" t="s">
+        <v>972</v>
       </c>
       <c r="C115" s="34" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D115" s="19" t="s">
-        <v>1032</v>
+        <v>1034</v>
+      </c>
+      <c r="D115" s="20" t="s">
+        <v>1035</v>
       </c>
       <c r="E115" s="12">
         <v>4.0</v>
       </c>
       <c r="F115" s="13" t="s">
-        <v>1033</v>
-      </c>
-      <c r="G115" s="16" t="s">
-        <v>929</v>
+        <v>1036</v>
+      </c>
+      <c r="G115" s="18" t="s">
+        <v>932</v>
       </c>
       <c r="H115" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I115" s="12">
         <v>2023.0</v>
       </c>
-      <c r="J115" s="19"/>
+      <c r="J115" s="20"/>
       <c r="K115" s="21" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="L115" s="21" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="M115" s="21" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="N115" s="21" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="O115" s="21" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="116" ht="75.0" customHeight="1">
-      <c r="A116" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B116" s="19" t="s">
-        <v>1039</v>
+      <c r="A116" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B116" s="20" t="s">
+        <v>1042</v>
       </c>
       <c r="C116" s="34" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D116" s="19" t="s">
-        <v>1041</v>
+        <v>1043</v>
+      </c>
+      <c r="D116" s="20" t="s">
+        <v>1044</v>
       </c>
       <c r="E116" s="12">
         <v>4.0</v>
       </c>
       <c r="F116" s="13" t="s">
-        <v>1042</v>
-      </c>
-      <c r="G116" s="23" t="s">
-        <v>1043</v>
+        <v>1045</v>
+      </c>
+      <c r="G116" s="26" t="s">
+        <v>1046</v>
       </c>
       <c r="H116" s="12" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="I116" s="12">
         <v>2025.0</v>
       </c>
       <c r="J116" s="13"/>
       <c r="K116" s="21" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="L116" s="21" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="M116" s="21" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="N116" s="21" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="O116" s="21" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="117" ht="75.0" customHeight="1">
-      <c r="A117" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B117" s="19" t="s">
-        <v>1039</v>
+      <c r="A117" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B117" s="20" t="s">
+        <v>1042</v>
       </c>
       <c r="C117" s="34" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D117" s="19" t="s">
-        <v>1050</v>
+        <v>1052</v>
+      </c>
+      <c r="D117" s="20" t="s">
+        <v>1053</v>
       </c>
       <c r="E117" s="12">
         <v>4.0</v>
       </c>
       <c r="F117" s="13" t="s">
-        <v>1051</v>
-      </c>
-      <c r="G117" s="23" t="s">
-        <v>1052</v>
+        <v>1054</v>
+      </c>
+      <c r="G117" s="26" t="s">
+        <v>1055</v>
       </c>
       <c r="H117" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I117" s="12">
         <v>2023.0</v>
       </c>
-      <c r="J117" s="19"/>
+      <c r="J117" s="20"/>
       <c r="K117" s="21" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="L117" s="21" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="M117" s="21" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="N117" s="21" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="O117" s="21" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="118" ht="75.0" customHeight="1">
-      <c r="A118" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B118" s="19" t="s">
-        <v>1039</v>
+      <c r="A118" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B118" s="20" t="s">
+        <v>1042</v>
       </c>
       <c r="C118" s="34" t="s">
-        <v>1058</v>
-      </c>
-      <c r="D118" s="19" t="s">
-        <v>1059</v>
+        <v>1061</v>
+      </c>
+      <c r="D118" s="20" t="s">
+        <v>1062</v>
       </c>
       <c r="E118" s="12">
         <v>4.0</v>
       </c>
       <c r="F118" s="13" t="s">
-        <v>1060</v>
-      </c>
-      <c r="G118" s="23" t="s">
-        <v>1061</v>
+        <v>1063</v>
+      </c>
+      <c r="G118" s="26" t="s">
+        <v>1064</v>
       </c>
       <c r="H118" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I118" s="12">
         <v>2025.0</v>
       </c>
       <c r="J118" s="13"/>
       <c r="K118" s="21" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="L118" s="21" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="M118" s="21" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="N118" s="21" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="O118" s="21" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="119" ht="75.0" customHeight="1">
-      <c r="A119" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B119" s="19" t="s">
-        <v>1039</v>
+      <c r="A119" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B119" s="20" t="s">
+        <v>1042</v>
       </c>
       <c r="C119" s="34" t="s">
-        <v>1067</v>
-      </c>
-      <c r="D119" s="19" t="s">
-        <v>1068</v>
+        <v>1070</v>
+      </c>
+      <c r="D119" s="20" t="s">
+        <v>1071</v>
       </c>
       <c r="E119" s="12" t="s">
         <v>44</v>
@@ -12046,47 +12075,47 @@
       <c r="F119" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G119" s="19"/>
-      <c r="H119" s="17"/>
-      <c r="I119" s="17"/>
-      <c r="J119" s="19"/>
+      <c r="G119" s="20"/>
+      <c r="H119" s="19"/>
+      <c r="I119" s="19"/>
+      <c r="J119" s="20"/>
       <c r="K119" s="21" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="L119" s="21" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="M119" s="21" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="N119" s="21" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="O119" s="21" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="120" ht="75.0" customHeight="1">
-      <c r="A120" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B120" s="19" t="s">
-        <v>1039</v>
+      <c r="A120" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B120" s="20" t="s">
+        <v>1042</v>
       </c>
       <c r="C120" s="34" t="s">
-        <v>1074</v>
-      </c>
-      <c r="D120" s="19" t="s">
-        <v>1075</v>
+        <v>1077</v>
+      </c>
+      <c r="D120" s="20" t="s">
+        <v>1078</v>
       </c>
       <c r="E120" s="12">
         <v>3.0</v>
       </c>
       <c r="F120" s="13" t="s">
-        <v>1076</v>
-      </c>
-      <c r="G120" s="23" t="s">
-        <v>1077</v>
+        <v>1079</v>
+      </c>
+      <c r="G120" s="26" t="s">
+        <v>1080</v>
       </c>
       <c r="H120" s="12">
         <v>72.0</v>
@@ -12096,33 +12125,33 @@
       </c>
       <c r="J120" s="13"/>
       <c r="K120" s="21" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="L120" s="21" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="M120" s="21" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="N120" s="21" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="O120" s="21" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="121" ht="75.0" customHeight="1">
-      <c r="A121" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B121" s="19" t="s">
-        <v>1039</v>
+      <c r="A121" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B121" s="20" t="s">
+        <v>1042</v>
       </c>
       <c r="C121" s="34" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D121" s="19" t="s">
-        <v>1084</v>
+        <v>1086</v>
+      </c>
+      <c r="D121" s="20" t="s">
+        <v>1087</v>
       </c>
       <c r="E121" s="12" t="s">
         <v>44</v>
@@ -12130,38 +12159,38 @@
       <c r="F121" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G121" s="19"/>
-      <c r="H121" s="17"/>
-      <c r="I121" s="17"/>
-      <c r="J121" s="19"/>
+      <c r="G121" s="20"/>
+      <c r="H121" s="19"/>
+      <c r="I121" s="19"/>
+      <c r="J121" s="20"/>
       <c r="K121" s="21" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="L121" s="21" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="M121" s="21" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="N121" s="21" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="O121" s="21" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="122" ht="75.0" customHeight="1">
-      <c r="A122" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B122" s="19" t="s">
-        <v>1039</v>
+      <c r="A122" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B122" s="20" t="s">
+        <v>1042</v>
       </c>
       <c r="C122" s="34" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D122" s="19" t="s">
-        <v>1091</v>
+        <v>1093</v>
+      </c>
+      <c r="D122" s="20" t="s">
+        <v>1094</v>
       </c>
       <c r="E122" s="12" t="s">
         <v>44</v>
@@ -12169,38 +12198,38 @@
       <c r="F122" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G122" s="19"/>
-      <c r="H122" s="17"/>
-      <c r="I122" s="17"/>
-      <c r="J122" s="19"/>
+      <c r="G122" s="20"/>
+      <c r="H122" s="19"/>
+      <c r="I122" s="19"/>
+      <c r="J122" s="20"/>
       <c r="K122" s="21" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="L122" s="21" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="M122" s="21" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="N122" s="21" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="O122" s="21" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="123" ht="75.0" customHeight="1">
-      <c r="A123" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B123" s="19" t="s">
-        <v>1039</v>
+      <c r="A123" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B123" s="20" t="s">
+        <v>1042</v>
       </c>
       <c r="C123" s="34" t="s">
-        <v>1097</v>
-      </c>
-      <c r="D123" s="19" t="s">
-        <v>1098</v>
+        <v>1100</v>
+      </c>
+      <c r="D123" s="20" t="s">
+        <v>1101</v>
       </c>
       <c r="E123" s="12" t="s">
         <v>44</v>
@@ -12208,38 +12237,38 @@
       <c r="F123" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G123" s="19"/>
-      <c r="H123" s="17"/>
-      <c r="I123" s="17"/>
-      <c r="J123" s="19"/>
+      <c r="G123" s="20"/>
+      <c r="H123" s="19"/>
+      <c r="I123" s="19"/>
+      <c r="J123" s="20"/>
       <c r="K123" s="21" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="L123" s="21" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="M123" s="21" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="N123" s="21" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="O123" s="21" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="124" ht="75.0" customHeight="1">
       <c r="A124" s="35" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B124" s="35" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="C124" s="36" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D124" s="35" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="E124" s="12" t="s">
         <v>44</v>
@@ -12247,357 +12276,357 @@
       <c r="F124" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G124" s="19"/>
-      <c r="H124" s="17"/>
-      <c r="I124" s="17"/>
-      <c r="J124" s="19"/>
+      <c r="G124" s="20"/>
+      <c r="H124" s="19"/>
+      <c r="I124" s="19"/>
+      <c r="J124" s="20"/>
       <c r="K124" s="21" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="L124" s="21" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="M124" s="21" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="N124" s="21" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="O124" s="21" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="125" ht="75.0" customHeight="1">
       <c r="A125" s="35" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B125" s="35" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="C125" s="36" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="D125" s="35" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="E125" s="12">
         <v>3.0</v>
       </c>
       <c r="F125" s="13" t="s">
-        <v>1114</v>
-      </c>
-      <c r="G125" s="16" t="s">
-        <v>1115</v>
+        <v>1117</v>
+      </c>
+      <c r="G125" s="18" t="s">
+        <v>1118</v>
       </c>
       <c r="H125" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I125" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J125" s="19"/>
+      <c r="J125" s="20"/>
       <c r="K125" s="21" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="L125" s="21" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="M125" s="21" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="N125" s="21" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="O125" s="21" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="126" ht="75.0" customHeight="1">
       <c r="A126" s="35" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B126" s="35" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="C126" s="36" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="D126" s="35" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="E126" s="12">
         <v>3.0</v>
       </c>
       <c r="F126" s="13" t="s">
-        <v>1123</v>
-      </c>
-      <c r="G126" s="16" t="s">
-        <v>1124</v>
+        <v>1126</v>
+      </c>
+      <c r="G126" s="18" t="s">
+        <v>1127</v>
       </c>
       <c r="H126" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I126" s="12">
         <v>2025.0</v>
       </c>
       <c r="J126" s="13"/>
       <c r="K126" s="21" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="L126" s="21" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="M126" s="21" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="N126" s="21" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="O126" s="21" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="127" ht="75.0" customHeight="1">
       <c r="A127" s="35" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B127" s="35" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="C127" s="36" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="D127" s="35" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="E127" s="12">
         <v>4.0</v>
       </c>
       <c r="F127" s="13" t="s">
-        <v>1132</v>
-      </c>
-      <c r="G127" s="23" t="s">
-        <v>1133</v>
+        <v>1135</v>
+      </c>
+      <c r="G127" s="26" t="s">
+        <v>1136</v>
       </c>
       <c r="H127" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I127" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J127" s="19"/>
+      <c r="J127" s="20"/>
       <c r="K127" s="21" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="L127" s="21" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="M127" s="21" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="N127" s="21" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="O127" s="21" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="128" ht="75.0" customHeight="1">
       <c r="A128" s="35" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B128" s="35" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="C128" s="36" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="D128" s="35" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="E128" s="12">
         <v>3.0</v>
       </c>
       <c r="F128" s="13" t="s">
-        <v>1141</v>
-      </c>
-      <c r="G128" s="23" t="s">
-        <v>1142</v>
+        <v>1144</v>
+      </c>
+      <c r="G128" s="26" t="s">
+        <v>1145</v>
       </c>
       <c r="H128" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I128" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J128" s="19"/>
+      <c r="J128" s="20"/>
       <c r="K128" s="21" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="L128" s="21" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="M128" s="21" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="N128" s="21" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="O128" s="21" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="129" ht="75.0" customHeight="1">
       <c r="A129" s="35" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B129" s="35" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="C129" s="36" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="D129" s="35" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="E129" s="12">
         <v>4.0</v>
       </c>
       <c r="F129" s="13" t="s">
-        <v>1150</v>
-      </c>
-      <c r="G129" s="23" t="s">
-        <v>1151</v>
+        <v>1153</v>
+      </c>
+      <c r="G129" s="26" t="s">
+        <v>1154</v>
       </c>
       <c r="H129" s="12" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="I129" s="12">
         <v>2026.0</v>
       </c>
       <c r="J129" s="13" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="K129" s="21" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="L129" s="21" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="M129" s="21" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="N129" s="21" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="O129" s="21" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="130" ht="75.0" customHeight="1">
       <c r="A130" s="35" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B130" s="35" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="C130" s="36" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="D130" s="35" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="E130" s="12">
         <v>3.0</v>
       </c>
       <c r="F130" s="13" t="s">
-        <v>1161</v>
-      </c>
-      <c r="G130" s="16" t="s">
-        <v>1115</v>
+        <v>1164</v>
+      </c>
+      <c r="G130" s="18" t="s">
+        <v>1118</v>
       </c>
       <c r="H130" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I130" s="12">
         <v>2025.0</v>
       </c>
       <c r="J130" s="13" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="K130" s="21" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="L130" s="21" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="M130" s="21" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="N130" s="21" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="O130" s="21" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="131" ht="75.0" customHeight="1">
       <c r="A131" s="35" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B131" s="35" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="C131" s="36" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="D131" s="35" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="E131" s="12">
         <v>3.0</v>
       </c>
       <c r="F131" s="13" t="s">
-        <v>1170</v>
-      </c>
-      <c r="G131" s="23" t="s">
-        <v>1171</v>
+        <v>1173</v>
+      </c>
+      <c r="G131" s="26" t="s">
+        <v>1174</v>
       </c>
       <c r="H131" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I131" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J131" s="19"/>
+      <c r="J131" s="20"/>
       <c r="K131" s="21" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="L131" s="21" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="M131" s="21" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="N131" s="21" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="O131" s="21" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="132" ht="75.0" customHeight="1">
       <c r="A132" s="35" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B132" s="35" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="C132" s="36" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="D132" s="35" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="E132" s="12" t="s">
         <v>44</v>
@@ -12605,128 +12634,128 @@
       <c r="F132" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G132" s="19"/>
-      <c r="H132" s="17"/>
-      <c r="I132" s="17"/>
-      <c r="J132" s="19"/>
+      <c r="G132" s="20"/>
+      <c r="H132" s="19"/>
+      <c r="I132" s="19"/>
+      <c r="J132" s="20"/>
       <c r="K132" s="21" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="L132" s="21" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="M132" s="21" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="N132" s="21" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="O132" s="21" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="133" ht="75.0" customHeight="1">
       <c r="A133" s="35" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B133" s="35" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="C133" s="36" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="D133" s="35" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="E133" s="12">
         <v>4.0</v>
       </c>
       <c r="F133" s="13" t="s">
-        <v>1187</v>
-      </c>
-      <c r="G133" s="23" t="s">
-        <v>1188</v>
+        <v>1190</v>
+      </c>
+      <c r="G133" s="26" t="s">
+        <v>1191</v>
       </c>
       <c r="H133" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I133" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J133" s="19"/>
+      <c r="J133" s="20"/>
       <c r="K133" s="21" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="L133" s="21" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="M133" s="21" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="N133" s="21" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="O133" s="21" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="134" ht="75.0" customHeight="1">
       <c r="A134" s="35" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B134" s="35" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="C134" s="36" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="D134" s="35" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="E134" s="12">
         <v>3.0</v>
       </c>
       <c r="F134" s="13" t="s">
-        <v>1196</v>
-      </c>
-      <c r="G134" s="23" t="s">
-        <v>1197</v>
+        <v>1199</v>
+      </c>
+      <c r="G134" s="26" t="s">
+        <v>1200</v>
       </c>
       <c r="H134" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I134" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J134" s="19"/>
+      <c r="J134" s="20"/>
       <c r="K134" s="21" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="L134" s="21" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="M134" s="21" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="N134" s="21" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="O134" s="21" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="135" ht="75.0" customHeight="1">
       <c r="A135" s="35" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B135" s="35" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="C135" s="36" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="D135" s="35" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="E135" s="12" t="s">
         <v>44</v>
@@ -12734,130 +12763,130 @@
       <c r="F135" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G135" s="19"/>
-      <c r="H135" s="17"/>
-      <c r="I135" s="17"/>
-      <c r="J135" s="19"/>
+      <c r="G135" s="20"/>
+      <c r="H135" s="19"/>
+      <c r="I135" s="19"/>
+      <c r="J135" s="20"/>
       <c r="K135" s="21" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="L135" s="21" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="M135" s="21" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="N135" s="21" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="O135" s="21" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="136" ht="75.0" customHeight="1">
       <c r="A136" s="35" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B136" s="35" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="C136" s="36" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="D136" s="35" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="E136" s="12">
         <v>4.0</v>
       </c>
       <c r="F136" s="13" t="s">
-        <v>1212</v>
-      </c>
-      <c r="G136" s="23" t="s">
-        <v>1213</v>
+        <v>1215</v>
+      </c>
+      <c r="G136" s="26" t="s">
+        <v>1216</v>
       </c>
       <c r="H136" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I136" s="12">
         <v>2025.0</v>
       </c>
-      <c r="J136" s="19"/>
+      <c r="J136" s="20"/>
       <c r="K136" s="21" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="L136" s="21" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="M136" s="21" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="N136" s="21" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="O136" s="21" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="137" ht="75.0" customHeight="1">
       <c r="A137" s="35" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B137" s="35" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="C137" s="36" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="D137" s="35" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="E137" s="12">
         <v>3.0</v>
       </c>
       <c r="F137" s="13" t="s">
-        <v>1221</v>
-      </c>
-      <c r="G137" s="23" t="s">
-        <v>1222</v>
+        <v>1224</v>
+      </c>
+      <c r="G137" s="26" t="s">
+        <v>1225</v>
       </c>
       <c r="H137" s="12" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="I137" s="12">
         <v>2025.0</v>
       </c>
       <c r="J137" s="13" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="K137" s="21" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="L137" s="21" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="M137" s="21" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="N137" s="21" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="O137" s="21" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="138" ht="75.0" customHeight="1">
       <c r="A138" s="35" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B138" s="35" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="C138" s="36" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="D138" s="35" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="E138" s="12" t="s">
         <v>44</v>
@@ -12865,159 +12894,159 @@
       <c r="F138" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G138" s="19"/>
-      <c r="H138" s="17"/>
-      <c r="I138" s="17"/>
-      <c r="J138" s="19"/>
+      <c r="G138" s="20"/>
+      <c r="H138" s="19"/>
+      <c r="I138" s="19"/>
+      <c r="J138" s="20"/>
       <c r="K138" s="21" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="L138" s="21" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="M138" s="21" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="N138" s="21" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="O138" s="21" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="139" ht="75.0" customHeight="1">
       <c r="A139" s="35" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B139" s="35" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="C139" s="36" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="D139" s="35" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="E139" s="12">
         <v>4.0</v>
       </c>
       <c r="F139" s="13" t="s">
-        <v>1238</v>
-      </c>
-      <c r="G139" s="16" t="s">
-        <v>1239</v>
+        <v>1241</v>
+      </c>
+      <c r="G139" s="18" t="s">
+        <v>1242</v>
       </c>
       <c r="H139" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I139" s="12">
         <v>2026.0</v>
       </c>
-      <c r="J139" s="19"/>
+      <c r="J139" s="20"/>
       <c r="K139" s="21" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="L139" s="21" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="M139" s="21" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="N139" s="21" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="O139" s="21" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="140" ht="75.0" customHeight="1">
       <c r="A140" s="35" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B140" s="35" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="C140" s="36" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="D140" s="35" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="E140" s="12">
         <v>4.0</v>
       </c>
       <c r="F140" s="13" t="s">
-        <v>1247</v>
-      </c>
-      <c r="G140" s="23" t="s">
-        <v>1248</v>
+        <v>1250</v>
+      </c>
+      <c r="G140" s="26" t="s">
+        <v>1251</v>
       </c>
       <c r="H140" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I140" s="12">
         <v>2026.0</v>
       </c>
-      <c r="J140" s="19"/>
+      <c r="J140" s="20"/>
       <c r="K140" s="21" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="L140" s="21" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="M140" s="21" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="N140" s="21" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="O140" s="21" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="141" ht="75.0" customHeight="1">
       <c r="A141" s="35" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B141" s="35" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="C141" s="36" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="D141" s="35" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="E141" s="12">
         <v>4.0</v>
       </c>
       <c r="F141" s="13" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G141" s="23" t="s">
-        <v>1257</v>
+        <v>1259</v>
+      </c>
+      <c r="G141" s="26" t="s">
+        <v>1260</v>
       </c>
       <c r="H141" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I141" s="12">
         <v>2026.0</v>
       </c>
-      <c r="J141" s="19"/>
+      <c r="J141" s="20"/>
       <c r="K141" s="21" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="L141" s="21" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="M141" s="21" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="N141" s="21" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="O141" s="21" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1"/>
@@ -13925,96 +13954,99 @@
     <hyperlink r:id="rId22" ref="G25"/>
     <hyperlink r:id="rId23" ref="G26"/>
     <hyperlink r:id="rId24" ref="G28"/>
-    <hyperlink r:id="rId25" ref="G30"/>
-    <hyperlink r:id="rId26" ref="G31"/>
-    <hyperlink r:id="rId27" ref="G34"/>
-    <hyperlink r:id="rId28" ref="G35"/>
-    <hyperlink r:id="rId29" ref="G36"/>
-    <hyperlink r:id="rId30" ref="G38"/>
-    <hyperlink r:id="rId31" ref="G40"/>
-    <hyperlink r:id="rId32" ref="G41"/>
-    <hyperlink r:id="rId33" ref="G42"/>
-    <hyperlink r:id="rId34" ref="G43"/>
-    <hyperlink r:id="rId35" ref="G44"/>
-    <hyperlink r:id="rId36" ref="G45"/>
-    <hyperlink r:id="rId37" ref="G46"/>
-    <hyperlink r:id="rId38" ref="G47"/>
-    <hyperlink r:id="rId39" ref="G48"/>
-    <hyperlink r:id="rId40" ref="G49"/>
-    <hyperlink r:id="rId41" ref="G50"/>
-    <hyperlink r:id="rId42" ref="G52"/>
-    <hyperlink r:id="rId43" ref="G55"/>
-    <hyperlink r:id="rId44" ref="G56"/>
-    <hyperlink r:id="rId45" ref="G57"/>
-    <hyperlink r:id="rId46" ref="G59"/>
-    <hyperlink r:id="rId47" ref="G60"/>
-    <hyperlink r:id="rId48" ref="G61"/>
-    <hyperlink r:id="rId49" ref="G62"/>
-    <hyperlink r:id="rId50" ref="G63"/>
-    <hyperlink r:id="rId51" ref="G64"/>
-    <hyperlink r:id="rId52" ref="G65"/>
-    <hyperlink r:id="rId53" ref="G66"/>
-    <hyperlink r:id="rId54" ref="G67"/>
-    <hyperlink r:id="rId55" ref="G68"/>
-    <hyperlink r:id="rId56" ref="G69"/>
-    <hyperlink r:id="rId57" ref="G70"/>
-    <hyperlink r:id="rId58" ref="G71"/>
-    <hyperlink r:id="rId59" ref="G74"/>
-    <hyperlink r:id="rId60" ref="G75"/>
-    <hyperlink r:id="rId61" ref="G77"/>
-    <hyperlink r:id="rId62" ref="G79"/>
-    <hyperlink r:id="rId63" ref="G80"/>
-    <hyperlink r:id="rId64" ref="G81"/>
-    <hyperlink r:id="rId65" ref="G82"/>
-    <hyperlink r:id="rId66" ref="G83"/>
-    <hyperlink r:id="rId67" ref="G84"/>
-    <hyperlink r:id="rId68" ref="G85"/>
-    <hyperlink r:id="rId69" ref="G86"/>
-    <hyperlink r:id="rId70" ref="G87"/>
-    <hyperlink r:id="rId71" ref="G88"/>
-    <hyperlink r:id="rId72" ref="G89"/>
-    <hyperlink r:id="rId73" ref="G90"/>
-    <hyperlink r:id="rId74" ref="G91"/>
-    <hyperlink r:id="rId75" ref="G93"/>
-    <hyperlink r:id="rId76" ref="G94"/>
-    <hyperlink r:id="rId77" ref="G97"/>
-    <hyperlink r:id="rId78" ref="G98"/>
-    <hyperlink r:id="rId79" ref="G100"/>
-    <hyperlink r:id="rId80" ref="G101"/>
-    <hyperlink r:id="rId81" ref="G102"/>
-    <hyperlink r:id="rId82" ref="G103"/>
-    <hyperlink r:id="rId83" ref="G104"/>
-    <hyperlink r:id="rId84" ref="G106"/>
-    <hyperlink r:id="rId85" ref="G108"/>
-    <hyperlink r:id="rId86" ref="G109"/>
-    <hyperlink r:id="rId87" ref="G110"/>
-    <hyperlink r:id="rId88" ref="G111"/>
-    <hyperlink r:id="rId89" ref="G112"/>
-    <hyperlink r:id="rId90" ref="G113"/>
-    <hyperlink r:id="rId91" ref="G114"/>
-    <hyperlink r:id="rId92" ref="G115"/>
-    <hyperlink r:id="rId93" ref="G116"/>
-    <hyperlink r:id="rId94" ref="G117"/>
-    <hyperlink r:id="rId95" ref="G118"/>
-    <hyperlink r:id="rId96" ref="G120"/>
-    <hyperlink r:id="rId97" ref="G125"/>
-    <hyperlink r:id="rId98" ref="G126"/>
-    <hyperlink r:id="rId99" ref="G127"/>
-    <hyperlink r:id="rId100" ref="G128"/>
-    <hyperlink r:id="rId101" ref="G129"/>
-    <hyperlink r:id="rId102" ref="G130"/>
-    <hyperlink r:id="rId103" ref="G131"/>
-    <hyperlink r:id="rId104" ref="G133"/>
-    <hyperlink r:id="rId105" ref="G134"/>
-    <hyperlink r:id="rId106" ref="G136"/>
-    <hyperlink r:id="rId107" ref="G137"/>
-    <hyperlink r:id="rId108" ref="G139"/>
-    <hyperlink r:id="rId109" ref="G140"/>
-    <hyperlink r:id="rId110" ref="G141"/>
+    <hyperlink r:id="rId25" ref="G29"/>
+    <hyperlink r:id="rId26" ref="G30"/>
+    <hyperlink r:id="rId27" ref="G31"/>
+    <hyperlink r:id="rId28" ref="G32"/>
+    <hyperlink r:id="rId29" ref="G33"/>
+    <hyperlink r:id="rId30" ref="G34"/>
+    <hyperlink r:id="rId31" ref="G35"/>
+    <hyperlink r:id="rId32" ref="G36"/>
+    <hyperlink r:id="rId33" ref="G38"/>
+    <hyperlink r:id="rId34" ref="G40"/>
+    <hyperlink r:id="rId35" ref="G41"/>
+    <hyperlink r:id="rId36" ref="G42"/>
+    <hyperlink r:id="rId37" ref="G43"/>
+    <hyperlink r:id="rId38" ref="G44"/>
+    <hyperlink r:id="rId39" ref="G45"/>
+    <hyperlink r:id="rId40" ref="G46"/>
+    <hyperlink r:id="rId41" ref="G47"/>
+    <hyperlink r:id="rId42" ref="G48"/>
+    <hyperlink r:id="rId43" ref="G49"/>
+    <hyperlink r:id="rId44" ref="G50"/>
+    <hyperlink r:id="rId45" ref="G52"/>
+    <hyperlink r:id="rId46" ref="G55"/>
+    <hyperlink r:id="rId47" ref="G56"/>
+    <hyperlink r:id="rId48" ref="G57"/>
+    <hyperlink r:id="rId49" ref="G59"/>
+    <hyperlink r:id="rId50" ref="G60"/>
+    <hyperlink r:id="rId51" ref="G61"/>
+    <hyperlink r:id="rId52" ref="G62"/>
+    <hyperlink r:id="rId53" ref="G63"/>
+    <hyperlink r:id="rId54" ref="G64"/>
+    <hyperlink r:id="rId55" ref="G65"/>
+    <hyperlink r:id="rId56" ref="G66"/>
+    <hyperlink r:id="rId57" ref="G67"/>
+    <hyperlink r:id="rId58" ref="G68"/>
+    <hyperlink r:id="rId59" ref="G69"/>
+    <hyperlink r:id="rId60" ref="G70"/>
+    <hyperlink r:id="rId61" ref="G71"/>
+    <hyperlink r:id="rId62" ref="G74"/>
+    <hyperlink r:id="rId63" ref="G75"/>
+    <hyperlink r:id="rId64" ref="G77"/>
+    <hyperlink r:id="rId65" ref="G79"/>
+    <hyperlink r:id="rId66" ref="G80"/>
+    <hyperlink r:id="rId67" ref="G81"/>
+    <hyperlink r:id="rId68" ref="G82"/>
+    <hyperlink r:id="rId69" ref="G83"/>
+    <hyperlink r:id="rId70" ref="G84"/>
+    <hyperlink r:id="rId71" ref="G85"/>
+    <hyperlink r:id="rId72" ref="G86"/>
+    <hyperlink r:id="rId73" ref="G87"/>
+    <hyperlink r:id="rId74" ref="G88"/>
+    <hyperlink r:id="rId75" ref="G89"/>
+    <hyperlink r:id="rId76" ref="G90"/>
+    <hyperlink r:id="rId77" ref="G91"/>
+    <hyperlink r:id="rId78" ref="G93"/>
+    <hyperlink r:id="rId79" ref="G94"/>
+    <hyperlink r:id="rId80" ref="G97"/>
+    <hyperlink r:id="rId81" ref="G98"/>
+    <hyperlink r:id="rId82" ref="G100"/>
+    <hyperlink r:id="rId83" ref="G101"/>
+    <hyperlink r:id="rId84" ref="G102"/>
+    <hyperlink r:id="rId85" ref="G103"/>
+    <hyperlink r:id="rId86" ref="G104"/>
+    <hyperlink r:id="rId87" ref="G106"/>
+    <hyperlink r:id="rId88" ref="G108"/>
+    <hyperlink r:id="rId89" ref="G109"/>
+    <hyperlink r:id="rId90" ref="G110"/>
+    <hyperlink r:id="rId91" ref="G111"/>
+    <hyperlink r:id="rId92" ref="G112"/>
+    <hyperlink r:id="rId93" ref="G113"/>
+    <hyperlink r:id="rId94" ref="G114"/>
+    <hyperlink r:id="rId95" ref="G115"/>
+    <hyperlink r:id="rId96" ref="G116"/>
+    <hyperlink r:id="rId97" ref="G117"/>
+    <hyperlink r:id="rId98" ref="G118"/>
+    <hyperlink r:id="rId99" ref="G120"/>
+    <hyperlink r:id="rId100" ref="G125"/>
+    <hyperlink r:id="rId101" ref="G126"/>
+    <hyperlink r:id="rId102" ref="G127"/>
+    <hyperlink r:id="rId103" ref="G128"/>
+    <hyperlink r:id="rId104" ref="G129"/>
+    <hyperlink r:id="rId105" ref="G130"/>
+    <hyperlink r:id="rId106" ref="G131"/>
+    <hyperlink r:id="rId107" ref="G133"/>
+    <hyperlink r:id="rId108" ref="G134"/>
+    <hyperlink r:id="rId109" ref="G136"/>
+    <hyperlink r:id="rId110" ref="G137"/>
+    <hyperlink r:id="rId111" ref="G139"/>
+    <hyperlink r:id="rId112" ref="G140"/>
+    <hyperlink r:id="rId113" ref="G141"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId111"/>
+  <drawing r:id="rId114"/>
 </worksheet>
 </file>